--- a/research/traditional_assets/database/data/argentina/argentina_transportation.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_transportation.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="base_auso" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,73 +590,79 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.3135</v>
+        <v>0.392</v>
+      </c>
+      <c r="E2">
+        <v>0.205</v>
       </c>
       <c r="G2">
-        <v>-0.8733826247689463</v>
+        <v>0.6152727272727272</v>
       </c>
       <c r="H2">
-        <v>-0.8733826247689463</v>
+        <v>0.6152727272727272</v>
       </c>
       <c r="I2">
-        <v>0.3465804066543438</v>
+        <v>0.4225454545454546</v>
       </c>
       <c r="J2">
-        <v>0.1732902033271719</v>
+        <v>0.4225454545454546</v>
       </c>
       <c r="K2">
-        <v>-13.33</v>
+        <v>10.9</v>
       </c>
       <c r="L2">
-        <v>-0.1231977818853974</v>
+        <v>0.07927272727272727</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01600587371512482</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01600587371512482</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.4</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>32.46</v>
+        <v>51.5</v>
       </c>
       <c r="V2">
-        <v>0.1997538461538462</v>
+        <v>0.1890602055800294</v>
       </c>
       <c r="W2">
-        <v>-0.08883903437686598</v>
+        <v>0.07605070740696707</v>
       </c>
       <c r="X2">
-        <v>0.1504740010131135</v>
+        <v>0.2610946041361314</v>
       </c>
       <c r="Y2">
-        <v>-0.2393130353899795</v>
+        <v>-0.1850438967291643</v>
       </c>
       <c r="Z2">
-        <v>0.6384987607695031</v>
+        <v>0.9231905465288036</v>
       </c>
       <c r="AA2">
-        <v>0.113820215066581</v>
+        <v>0.4108111029330038</v>
       </c>
       <c r="AB2">
-        <v>0.1504740010131135</v>
+        <v>0.2610946041361314</v>
       </c>
       <c r="AC2">
-        <v>-0.03665378594653253</v>
+        <v>0.1497164987968724</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-32.46</v>
+        <v>-51.5</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,25 +683,28 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2496155029221778</v>
+        <v>-0.2331371661385243</v>
       </c>
       <c r="AK2">
-        <v>-0.2179401101114543</v>
+        <v>-0.2973441108545035</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AM2">
-        <v>-31.7</v>
+        <v>-7.57</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
+      <c r="AO2">
+        <v>1162</v>
+      </c>
       <c r="AP2">
-        <v>-0.8115</v>
+        <v>-0.8554817275747508</v>
       </c>
       <c r="AQ2">
-        <v>-1.182965299684543</v>
+        <v>-7.675033025099075</v>
       </c>
     </row>
     <row r="3">
@@ -713,25 +724,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.351</v>
+        <v>0.369</v>
+      </c>
+      <c r="E3">
+        <v>0.242</v>
       </c>
       <c r="G3">
-        <v>-0.9601593625498008</v>
+        <v>0.4905660377358491</v>
       </c>
       <c r="H3">
-        <v>-0.9601593625498008</v>
+        <v>0.4905660377358491</v>
       </c>
       <c r="I3">
-        <v>0.2928286852589641</v>
+        <v>0.3754716981132075</v>
       </c>
       <c r="J3">
-        <v>0.1464143426294821</v>
+        <v>0.3754716981132075</v>
       </c>
       <c r="K3">
-        <v>-8.17</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>-0.1627490039840637</v>
+        <v>0.1113207547169811</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,7 +754,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -749,37 +763,37 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>8.76</v>
+        <v>18.6</v>
       </c>
       <c r="V3">
-        <v>0.1377358490566038</v>
+        <v>0.2</v>
       </c>
       <c r="W3">
-        <v>-0.1324149108589951</v>
+        <v>0.1134615384615385</v>
       </c>
       <c r="X3">
-        <v>0.1504740010131135</v>
+        <v>0.2610946041361314</v>
       </c>
       <c r="Y3">
-        <v>-0.2828889118721086</v>
+        <v>-0.1476330656745929</v>
       </c>
       <c r="Z3">
-        <v>0.8491204330175913</v>
+        <v>1.225716928769658</v>
       </c>
       <c r="AA3">
-        <v>0.1243234100135318</v>
+        <v>0.4602220166512488</v>
       </c>
       <c r="AB3">
-        <v>0.1504740010131135</v>
+        <v>0.2610946041361314</v>
       </c>
       <c r="AC3">
-        <v>-0.02615059099958175</v>
+        <v>0.1991274125151174</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -791,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-8.76</v>
+        <v>-18.6</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -800,10 +814,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1597374179431072</v>
+        <v>-0.25</v>
       </c>
       <c r="AK3">
-        <v>-0.2025901942645698</v>
+        <v>-0.379591836734694</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -815,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.5615384615384615</v>
+        <v>-0.9073170731707317</v>
       </c>
     </row>
     <row r="4">
@@ -835,73 +849,79 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.276</v>
+        <v>0.415</v>
+      </c>
+      <c r="E4">
+        <v>0.168</v>
       </c>
       <c r="G4">
-        <v>-0.7982758620689655</v>
+        <v>0.6934911242603551</v>
       </c>
       <c r="H4">
-        <v>-0.7982758620689655</v>
+        <v>0.6934911242603551</v>
       </c>
       <c r="I4">
-        <v>0.3931034482758621</v>
+        <v>0.4520710059171598</v>
       </c>
       <c r="J4">
-        <v>0.196551724137931</v>
+        <v>0.4520710059171598</v>
       </c>
       <c r="K4">
-        <v>-5.16</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-0.08896551724137931</v>
+        <v>0.05917159763313609</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>4.36</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02430323299888517</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.8720000000000001</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>4.36</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02430323299888517</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.8720000000000001</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>23.7</v>
+        <v>32.9</v>
       </c>
       <c r="V4">
-        <v>0.2396359959555106</v>
+        <v>0.1833890746934225</v>
       </c>
       <c r="W4">
-        <v>-0.04526315789473685</v>
+        <v>0.03863987635239567</v>
       </c>
       <c r="X4">
-        <v>0.1504740010131135</v>
+        <v>0.2610946041361314</v>
       </c>
       <c r="Y4">
-        <v>-0.1957371589078504</v>
+        <v>-0.2224547277837357</v>
       </c>
       <c r="Z4">
-        <v>0.5256479970998731</v>
+        <v>0.7994323557237464</v>
       </c>
       <c r="AA4">
-        <v>0.1033170201196302</v>
+        <v>0.3614001892147587</v>
       </c>
       <c r="AB4">
-        <v>0.1504740010131135</v>
+        <v>0.2610946041361314</v>
       </c>
       <c r="AC4">
-        <v>-0.0471569808934833</v>
+        <v>0.1003055850786274</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -913,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-23.7</v>
+        <v>-32.9</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -922,25 +942,8740 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.3151595744680851</v>
+        <v>-0.2245733788395904</v>
       </c>
       <c r="AK4">
-        <v>-0.2242194891201514</v>
+        <v>-0.2648953301127214</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AM4">
-        <v>-31.7</v>
+        <v>-7.57</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
+      <c r="AO4">
+        <v>764</v>
+      </c>
       <c r="AP4">
-        <v>-0.9713114754098361</v>
+        <v>-0.8287153652392946</v>
       </c>
       <c r="AQ4">
-        <v>-0.719242902208202</v>
+        <v>-5.046235138705416</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Autopistas Del Sol SA (BASE:AUSO)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BASE:AUSO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Transportation</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.97</v>
+      </c>
+      <c r="G2">
+        <v>179.4</v>
+      </c>
+      <c r="H2">
+        <v>81.5368246378428</v>
+      </c>
+      <c r="I2">
+        <v>146.5</v>
+      </c>
+      <c r="J2">
+        <v>222.654824637843</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>174.018</v>
+      </c>
+      <c r="M2">
+        <v>0.261094604136131</v>
+      </c>
+      <c r="N2">
+        <v>0.185062986031915</v>
+      </c>
+      <c r="O2">
+        <v>0.131187740825688</v>
+      </c>
+      <c r="P2">
+        <v>0.03822</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.261094604136131</v>
+      </c>
+      <c r="T2">
+        <v>4.93298620106382</v>
+      </c>
+      <c r="U2">
+        <v>0.834876087904329</v>
+      </c>
+      <c r="V2">
+        <v>18.3811885353603</v>
+      </c>
+      <c r="W2">
+        <v>4.028436185700706</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>179.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.2662605952628563</v>
+      </c>
+      <c r="AC2">
+        <v>0.2018272935779817</v>
+      </c>
+      <c r="AD2">
+        <v>0.35</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>39.7</v>
+      </c>
+      <c r="AH2">
+        <v>-1.52</v>
+      </c>
+      <c r="AI2">
+        <v>1.580000000000005</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>0.05</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>32.9</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.2610946041361314</v>
+      </c>
+      <c r="C2">
+        <v>179.4</v>
+      </c>
+      <c r="D2">
+        <v>146.5</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>32.9</v>
+      </c>
+      <c r="H2">
+        <v>179.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>39.7</v>
+      </c>
+      <c r="K2">
+        <v>-1.52</v>
+      </c>
+      <c r="L2">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="O2">
+        <v>14.427</v>
+      </c>
+      <c r="P2">
+        <v>26.79300000000001</v>
+      </c>
+      <c r="Q2">
+        <v>25.27300000000001</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.2610946041361314</v>
+      </c>
+      <c r="T2">
+        <v>0.8348760879043289</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.35</v>
+      </c>
+      <c r="W2">
+        <v>0.029705</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.260225623021655</v>
+      </c>
+      <c r="C3">
+        <v>178.1809367735023</v>
+      </c>
+      <c r="D3">
+        <v>147.0749367735023</v>
+      </c>
+      <c r="E3">
+        <v>1.794</v>
+      </c>
+      <c r="F3">
+        <v>1.794</v>
+      </c>
+      <c r="G3">
+        <v>32.9</v>
+      </c>
+      <c r="H3">
+        <v>179.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>39.7</v>
+      </c>
+      <c r="K3">
+        <v>-1.52</v>
+      </c>
+      <c r="L3">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.08198580000000001</v>
+      </c>
+      <c r="N3">
+        <v>41.13801420000001</v>
+      </c>
+      <c r="O3">
+        <v>14.39830497</v>
+      </c>
+      <c r="P3">
+        <v>26.73970923000001</v>
+      </c>
+      <c r="Q3">
+        <v>25.21970923000001</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.2625541141632878</v>
+      </c>
+      <c r="T3">
+        <v>0.8403575975723877</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.35</v>
+      </c>
+      <c r="W3">
+        <v>0.029705</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>502.7699918766421</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.2593566419071785</v>
+      </c>
+      <c r="C4">
+        <v>176.9664039859328</v>
+      </c>
+      <c r="D4">
+        <v>147.6544039859328</v>
+      </c>
+      <c r="E4">
+        <v>3.588</v>
+      </c>
+      <c r="F4">
+        <v>3.588</v>
+      </c>
+      <c r="G4">
+        <v>32.9</v>
+      </c>
+      <c r="H4">
+        <v>179.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>39.7</v>
+      </c>
+      <c r="K4">
+        <v>-1.52</v>
+      </c>
+      <c r="L4">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.1639716</v>
+      </c>
+      <c r="N4">
+        <v>41.0560284</v>
+      </c>
+      <c r="O4">
+        <v>14.36960994</v>
+      </c>
+      <c r="P4">
+        <v>26.68641846</v>
+      </c>
+      <c r="Q4">
+        <v>25.16641846</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.2640434101093658</v>
+      </c>
+      <c r="T4">
+        <v>0.8459509747846925</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.35</v>
+      </c>
+      <c r="W4">
+        <v>0.029705</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>251.384995938321</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.258487660792702</v>
+      </c>
+      <c r="C5">
+        <v>175.7564553981518</v>
+      </c>
+      <c r="D5">
+        <v>148.2384553981518</v>
+      </c>
+      <c r="E5">
+        <v>5.382</v>
+      </c>
+      <c r="F5">
+        <v>5.382</v>
+      </c>
+      <c r="G5">
+        <v>32.9</v>
+      </c>
+      <c r="H5">
+        <v>179.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>39.7</v>
+      </c>
+      <c r="K5">
+        <v>-1.52</v>
+      </c>
+      <c r="L5">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.2459574</v>
+      </c>
+      <c r="N5">
+        <v>40.9740426</v>
+      </c>
+      <c r="O5">
+        <v>14.34091491</v>
+      </c>
+      <c r="P5">
+        <v>26.63312769</v>
+      </c>
+      <c r="Q5">
+        <v>25.11312769</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.2655634131883525</v>
+      </c>
+      <c r="T5">
+        <v>0.8516596793621993</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.35</v>
+      </c>
+      <c r="W5">
+        <v>0.029705</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>167.589997292214</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.2576186796782255</v>
+      </c>
+      <c r="C6">
+        <v>174.551145625008</v>
+      </c>
+      <c r="D6">
+        <v>148.827145625008</v>
+      </c>
+      <c r="E6">
+        <v>7.176</v>
+      </c>
+      <c r="F6">
+        <v>7.176</v>
+      </c>
+      <c r="G6">
+        <v>32.9</v>
+      </c>
+      <c r="H6">
+        <v>179.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>39.7</v>
+      </c>
+      <c r="K6">
+        <v>-1.52</v>
+      </c>
+      <c r="L6">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M6">
+        <v>0.3279432</v>
+      </c>
+      <c r="N6">
+        <v>40.89205680000001</v>
+      </c>
+      <c r="O6">
+        <v>14.31221988</v>
+      </c>
+      <c r="P6">
+        <v>26.57983692000001</v>
+      </c>
+      <c r="Q6">
+        <v>25.05983692000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.2671150829981516</v>
+      </c>
+      <c r="T6">
+        <v>0.8574873152850712</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.35</v>
+      </c>
+      <c r="W6">
+        <v>0.029705</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>125.6924979691605</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.2567496985637491</v>
+      </c>
+      <c r="C7">
+        <v>173.3505301523637</v>
+      </c>
+      <c r="D7">
+        <v>149.4205301523637</v>
+      </c>
+      <c r="E7">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="F7">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="G7">
+        <v>32.9</v>
+      </c>
+      <c r="H7">
+        <v>179.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>39.7</v>
+      </c>
+      <c r="K7">
+        <v>-1.52</v>
+      </c>
+      <c r="L7">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.409929</v>
+      </c>
+      <c r="N7">
+        <v>40.81007100000001</v>
+      </c>
+      <c r="O7">
+        <v>14.28352485</v>
+      </c>
+      <c r="P7">
+        <v>26.52654615000001</v>
+      </c>
+      <c r="Q7">
+        <v>25.00654615000001</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.2686994195407885</v>
+      </c>
+      <c r="T7">
+        <v>0.8634376382800033</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.35</v>
+      </c>
+      <c r="W7">
+        <v>0.029705</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>100.5539983753284</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2558807174492727</v>
+      </c>
+      <c r="C8">
+        <v>172.1546653545278</v>
+      </c>
+      <c r="D8">
+        <v>150.0186653545278</v>
+      </c>
+      <c r="E8">
+        <v>10.764</v>
+      </c>
+      <c r="F8">
+        <v>10.764</v>
+      </c>
+      <c r="G8">
+        <v>32.9</v>
+      </c>
+      <c r="H8">
+        <v>179.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>39.7</v>
+      </c>
+      <c r="K8">
+        <v>-1.52</v>
+      </c>
+      <c r="L8">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M8">
+        <v>0.4919148</v>
+      </c>
+      <c r="N8">
+        <v>40.7280852</v>
+      </c>
+      <c r="O8">
+        <v>14.25482982</v>
+      </c>
+      <c r="P8">
+        <v>26.47325538</v>
+      </c>
+      <c r="Q8">
+        <v>24.95325538000001</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.2703174653715666</v>
+      </c>
+      <c r="T8">
+        <v>0.8695145638918489</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.35</v>
+      </c>
+      <c r="W8">
+        <v>0.029705</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>83.794998646107</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2550117363347961</v>
+      </c>
+      <c r="C9">
+        <v>170.9636085121102</v>
+      </c>
+      <c r="D9">
+        <v>150.6216085121102</v>
+      </c>
+      <c r="E9">
+        <v>12.558</v>
+      </c>
+      <c r="F9">
+        <v>12.558</v>
+      </c>
+      <c r="G9">
+        <v>32.9</v>
+      </c>
+      <c r="H9">
+        <v>179.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>39.7</v>
+      </c>
+      <c r="K9">
+        <v>-1.52</v>
+      </c>
+      <c r="L9">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M9">
+        <v>0.5739006000000001</v>
+      </c>
+      <c r="N9">
+        <v>40.6460994</v>
+      </c>
+      <c r="O9">
+        <v>14.22613479</v>
+      </c>
+      <c r="P9">
+        <v>26.41996461</v>
+      </c>
+      <c r="Q9">
+        <v>24.89996461</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.2719703078868776</v>
+      </c>
+      <c r="T9">
+        <v>0.8757221760759922</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.35</v>
+      </c>
+      <c r="W9">
+        <v>0.029705</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>71.82428455380601</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2541427552203196</v>
+      </c>
+      <c r="C10">
+        <v>169.777417830307</v>
+      </c>
+      <c r="D10">
+        <v>151.229417830307</v>
+      </c>
+      <c r="E10">
+        <v>14.352</v>
+      </c>
+      <c r="F10">
+        <v>14.352</v>
+      </c>
+      <c r="G10">
+        <v>32.9</v>
+      </c>
+      <c r="H10">
+        <v>179.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>39.7</v>
+      </c>
+      <c r="K10">
+        <v>-1.52</v>
+      </c>
+      <c r="L10">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.6558864000000001</v>
+      </c>
+      <c r="N10">
+        <v>40.56411360000001</v>
+      </c>
+      <c r="O10">
+        <v>14.19743976</v>
+      </c>
+      <c r="P10">
+        <v>26.36667384</v>
+      </c>
+      <c r="Q10">
+        <v>24.84667384</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.273659081761217</v>
+      </c>
+      <c r="T10">
+        <v>0.8820647363510952</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.35</v>
+      </c>
+      <c r="W10">
+        <v>0.029705</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>62.84624898458026</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2532737741058433</v>
+      </c>
+      <c r="C11">
+        <v>168.5961524576323</v>
+      </c>
+      <c r="D11">
+        <v>151.8421524576323</v>
+      </c>
+      <c r="E11">
+        <v>16.146</v>
+      </c>
+      <c r="F11">
+        <v>16.146</v>
+      </c>
+      <c r="G11">
+        <v>32.9</v>
+      </c>
+      <c r="H11">
+        <v>179.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>39.7</v>
+      </c>
+      <c r="K11">
+        <v>-1.52</v>
+      </c>
+      <c r="L11">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M11">
+        <v>0.7378722000000001</v>
+      </c>
+      <c r="N11">
+        <v>40.48212780000001</v>
+      </c>
+      <c r="O11">
+        <v>14.16874473</v>
+      </c>
+      <c r="P11">
+        <v>26.31338307000001</v>
+      </c>
+      <c r="Q11">
+        <v>24.79338307000001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.2753849715448827</v>
+      </c>
+      <c r="T11">
+        <v>0.8885466935553215</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.35</v>
+      </c>
+      <c r="W11">
+        <v>0.029705</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>55.86333243073801</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2524047929913668</v>
+      </c>
+      <c r="C12">
+        <v>167.4198725051056</v>
+      </c>
+      <c r="D12">
+        <v>152.4598725051056</v>
+      </c>
+      <c r="E12">
+        <v>17.94</v>
+      </c>
+      <c r="F12">
+        <v>17.94</v>
+      </c>
+      <c r="G12">
+        <v>32.9</v>
+      </c>
+      <c r="H12">
+        <v>179.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>39.7</v>
+      </c>
+      <c r="K12">
+        <v>-1.52</v>
+      </c>
+      <c r="L12">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.8198580000000001</v>
+      </c>
+      <c r="N12">
+        <v>40.400142</v>
+      </c>
+      <c r="O12">
+        <v>14.1400497</v>
+      </c>
+      <c r="P12">
+        <v>26.2600923</v>
+      </c>
+      <c r="Q12">
+        <v>24.7400923</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.277149214434852</v>
+      </c>
+      <c r="T12">
+        <v>0.8951726942529749</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.35</v>
+      </c>
+      <c r="W12">
+        <v>0.029705</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>50.2769991876642</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2515358118768903</v>
+      </c>
+      <c r="C13">
+        <v>166.2486390659096</v>
+      </c>
+      <c r="D13">
+        <v>153.0826390659096</v>
+      </c>
+      <c r="E13">
+        <v>19.734</v>
+      </c>
+      <c r="F13">
+        <v>19.734</v>
+      </c>
+      <c r="G13">
+        <v>32.9</v>
+      </c>
+      <c r="H13">
+        <v>179.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>39.7</v>
+      </c>
+      <c r="K13">
+        <v>-1.52</v>
+      </c>
+      <c r="L13">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.9018438000000002</v>
+      </c>
+      <c r="N13">
+        <v>40.3181562</v>
+      </c>
+      <c r="O13">
+        <v>14.11135467</v>
+      </c>
+      <c r="P13">
+        <v>26.20680153</v>
+      </c>
+      <c r="Q13">
+        <v>24.68680153</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.278953103232461</v>
+      </c>
+      <c r="T13">
+        <v>0.9019475938427104</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.35</v>
+      </c>
+      <c r="W13">
+        <v>0.029705</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>45.70636289787655</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2506668307624139</v>
+      </c>
+      <c r="C14">
+        <v>165.0825142355329</v>
+      </c>
+      <c r="D14">
+        <v>153.7105142355329</v>
+      </c>
+      <c r="E14">
+        <v>21.528</v>
+      </c>
+      <c r="F14">
+        <v>21.528</v>
+      </c>
+      <c r="G14">
+        <v>32.9</v>
+      </c>
+      <c r="H14">
+        <v>179.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>39.7</v>
+      </c>
+      <c r="K14">
+        <v>-1.52</v>
+      </c>
+      <c r="L14">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M14">
+        <v>0.9838296000000001</v>
+      </c>
+      <c r="N14">
+        <v>40.23617040000001</v>
+      </c>
+      <c r="O14">
+        <v>14.08265964</v>
+      </c>
+      <c r="P14">
+        <v>26.15351076</v>
+      </c>
+      <c r="Q14">
+        <v>24.63351076</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.280797989502743</v>
+      </c>
+      <c r="T14">
+        <v>0.9088764684231216</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.35</v>
+      </c>
+      <c r="W14">
+        <v>0.029705</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>41.89749932305351</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2497978496479374</v>
+      </c>
+      <c r="C15">
+        <v>163.9215611324089</v>
+      </c>
+      <c r="D15">
+        <v>154.3435611324089</v>
+      </c>
+      <c r="E15">
+        <v>23.322</v>
+      </c>
+      <c r="F15">
+        <v>23.322</v>
+      </c>
+      <c r="G15">
+        <v>32.9</v>
+      </c>
+      <c r="H15">
+        <v>179.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>39.7</v>
+      </c>
+      <c r="K15">
+        <v>-1.52</v>
+      </c>
+      <c r="L15">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M15">
+        <v>1.0658154</v>
+      </c>
+      <c r="N15">
+        <v>40.15418460000001</v>
+      </c>
+      <c r="O15">
+        <v>14.05396461</v>
+      </c>
+      <c r="P15">
+        <v>26.10021999000001</v>
+      </c>
+      <c r="Q15">
+        <v>24.58021999000001</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.2826852869516522</v>
+      </c>
+      <c r="T15">
+        <v>0.9159646274766459</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.35</v>
+      </c>
+      <c r="W15">
+        <v>0.029705</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>38.67461475974169</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2489288685334609</v>
+      </c>
+      <c r="C16">
+        <v>162.7658439190682</v>
+      </c>
+      <c r="D16">
+        <v>154.9818439190682</v>
+      </c>
+      <c r="E16">
+        <v>25.116</v>
+      </c>
+      <c r="F16">
+        <v>25.116</v>
+      </c>
+      <c r="G16">
+        <v>32.9</v>
+      </c>
+      <c r="H16">
+        <v>179.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>39.7</v>
+      </c>
+      <c r="K16">
+        <v>-1.52</v>
+      </c>
+      <c r="L16">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M16">
+        <v>1.1478012</v>
+      </c>
+      <c r="N16">
+        <v>40.0721988</v>
+      </c>
+      <c r="O16">
+        <v>14.02526958</v>
+      </c>
+      <c r="P16">
+        <v>26.04692922</v>
+      </c>
+      <c r="Q16">
+        <v>24.52692922</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2846164750389081</v>
+      </c>
+      <c r="T16">
+        <v>0.9232176274383916</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.35</v>
+      </c>
+      <c r="W16">
+        <v>0.029705</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>35.912142276903</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2480598874189845</v>
+      </c>
+      <c r="C17">
+        <v>161.615427823817</v>
+      </c>
+      <c r="D17">
+        <v>155.625427823817</v>
+      </c>
+      <c r="E17">
+        <v>26.91</v>
+      </c>
+      <c r="F17">
+        <v>26.91</v>
+      </c>
+      <c r="G17">
+        <v>32.9</v>
+      </c>
+      <c r="H17">
+        <v>179.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>39.7</v>
+      </c>
+      <c r="K17">
+        <v>-1.52</v>
+      </c>
+      <c r="L17">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M17">
+        <v>1.229787</v>
+      </c>
+      <c r="N17">
+        <v>39.990213</v>
+      </c>
+      <c r="O17">
+        <v>13.99657455</v>
+      </c>
+      <c r="P17">
+        <v>25.99363845000001</v>
+      </c>
+      <c r="Q17">
+        <v>24.47363845000001</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.2865931028458641</v>
+      </c>
+      <c r="T17">
+        <v>0.9306412862227667</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.35</v>
+      </c>
+      <c r="W17">
+        <v>0.029705</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>33.5179994584428</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.247190906304508</v>
+      </c>
+      <c r="C18">
+        <v>160.4703791629585</v>
+      </c>
+      <c r="D18">
+        <v>156.2743791629585</v>
+      </c>
+      <c r="E18">
+        <v>28.704</v>
+      </c>
+      <c r="F18">
+        <v>28.704</v>
+      </c>
+      <c r="G18">
+        <v>32.9</v>
+      </c>
+      <c r="H18">
+        <v>179.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>39.7</v>
+      </c>
+      <c r="K18">
+        <v>-1.52</v>
+      </c>
+      <c r="L18">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M18">
+        <v>1.3117728</v>
+      </c>
+      <c r="N18">
+        <v>39.90822720000001</v>
+      </c>
+      <c r="O18">
+        <v>13.96787952</v>
+      </c>
+      <c r="P18">
+        <v>25.94034768</v>
+      </c>
+      <c r="Q18">
+        <v>24.42034768</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2886167932196524</v>
+      </c>
+      <c r="T18">
+        <v>0.938241698787722</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.35</v>
+      </c>
+      <c r="W18">
+        <v>0.029705</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>31.42312449229013</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2463219251900315</v>
+      </c>
+      <c r="C19">
+        <v>159.3307653635722</v>
+      </c>
+      <c r="D19">
+        <v>156.9287653635722</v>
+      </c>
+      <c r="E19">
+        <v>30.498</v>
+      </c>
+      <c r="F19">
+        <v>30.498</v>
+      </c>
+      <c r="G19">
+        <v>32.9</v>
+      </c>
+      <c r="H19">
+        <v>179.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>39.7</v>
+      </c>
+      <c r="K19">
+        <v>-1.52</v>
+      </c>
+      <c r="L19">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M19">
+        <v>1.3937586</v>
+      </c>
+      <c r="N19">
+        <v>39.82624140000001</v>
+      </c>
+      <c r="O19">
+        <v>13.93918449</v>
+      </c>
+      <c r="P19">
+        <v>25.88705691000001</v>
+      </c>
+      <c r="Q19">
+        <v>24.36705691000001</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2906892472169055</v>
+      </c>
+      <c r="T19">
+        <v>0.9460252538241221</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.35</v>
+      </c>
+      <c r="W19">
+        <v>0.029705</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>29.57470540450835</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2454529440755551</v>
+      </c>
+      <c r="C20">
+        <v>158.1966549868683</v>
+      </c>
+      <c r="D20">
+        <v>157.5886549868683</v>
+      </c>
+      <c r="E20">
+        <v>32.292</v>
+      </c>
+      <c r="F20">
+        <v>32.292</v>
+      </c>
+      <c r="G20">
+        <v>32.9</v>
+      </c>
+      <c r="H20">
+        <v>179.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>39.7</v>
+      </c>
+      <c r="K20">
+        <v>-1.52</v>
+      </c>
+      <c r="L20">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M20">
+        <v>1.4757444</v>
+      </c>
+      <c r="N20">
+        <v>39.7442556</v>
+      </c>
+      <c r="O20">
+        <v>13.91048946</v>
+      </c>
+      <c r="P20">
+        <v>25.83376614</v>
+      </c>
+      <c r="Q20">
+        <v>24.31376614</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2928122488726282</v>
+      </c>
+      <c r="T20">
+        <v>0.9539986516662879</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.35</v>
+      </c>
+      <c r="W20">
+        <v>0.029705</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>27.931666215369</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2445839629610787</v>
+      </c>
+      <c r="C21">
+        <v>157.0681177521336</v>
+      </c>
+      <c r="D21">
+        <v>158.2541177521336</v>
+      </c>
+      <c r="E21">
+        <v>34.086</v>
+      </c>
+      <c r="F21">
+        <v>34.086</v>
+      </c>
+      <c r="G21">
+        <v>32.9</v>
+      </c>
+      <c r="H21">
+        <v>179.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>39.7</v>
+      </c>
+      <c r="K21">
+        <v>-1.52</v>
+      </c>
+      <c r="L21">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M21">
+        <v>1.5577302</v>
+      </c>
+      <c r="N21">
+        <v>39.6622698</v>
+      </c>
+      <c r="O21">
+        <v>13.88179443</v>
+      </c>
+      <c r="P21">
+        <v>25.78047537</v>
+      </c>
+      <c r="Q21">
+        <v>24.26047537000001</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2949876703223193</v>
+      </c>
+      <c r="T21">
+        <v>0.9621689235292482</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.35</v>
+      </c>
+      <c r="W21">
+        <v>0.029705</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>26.46157851982327</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2437149818466022</v>
+      </c>
+      <c r="C22">
+        <v>155.9452245612867</v>
+      </c>
+      <c r="D22">
+        <v>158.9252245612867</v>
+      </c>
+      <c r="E22">
+        <v>35.88</v>
+      </c>
+      <c r="F22">
+        <v>35.88</v>
+      </c>
+      <c r="G22">
+        <v>32.9</v>
+      </c>
+      <c r="H22">
+        <v>179.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>39.7</v>
+      </c>
+      <c r="K22">
+        <v>-1.52</v>
+      </c>
+      <c r="L22">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M22">
+        <v>1.639716</v>
+      </c>
+      <c r="N22">
+        <v>39.58028400000001</v>
+      </c>
+      <c r="O22">
+        <v>13.8530994</v>
+      </c>
+      <c r="P22">
+        <v>25.7271846</v>
+      </c>
+      <c r="Q22">
+        <v>24.20718460000001</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2972174773082528</v>
+      </c>
+      <c r="T22">
+        <v>0.9705434521887824</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.35</v>
+      </c>
+      <c r="W22">
+        <v>0.029705</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>25.1384995938321</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2428460007321257</v>
+      </c>
+      <c r="C23">
+        <v>154.8280475240607</v>
+      </c>
+      <c r="D23">
+        <v>159.6020475240607</v>
+      </c>
+      <c r="E23">
+        <v>37.674</v>
+      </c>
+      <c r="F23">
+        <v>37.674</v>
+      </c>
+      <c r="G23">
+        <v>32.9</v>
+      </c>
+      <c r="H23">
+        <v>179.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>39.7</v>
+      </c>
+      <c r="K23">
+        <v>-1.52</v>
+      </c>
+      <c r="L23">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M23">
+        <v>1.7217018</v>
+      </c>
+      <c r="N23">
+        <v>39.49829820000001</v>
+      </c>
+      <c r="O23">
+        <v>13.82440437</v>
+      </c>
+      <c r="P23">
+        <v>25.67389383</v>
+      </c>
+      <c r="Q23">
+        <v>24.15389383</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2995037351039566</v>
+      </c>
+      <c r="T23">
+        <v>0.9791299942321022</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.35</v>
+      </c>
+      <c r="W23">
+        <v>0.029705</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>23.941428184602</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2419770196176493</v>
+      </c>
+      <c r="C24">
+        <v>153.7166599838318</v>
+      </c>
+      <c r="D24">
+        <v>160.2846599838319</v>
+      </c>
+      <c r="E24">
+        <v>39.468</v>
+      </c>
+      <c r="F24">
+        <v>39.468</v>
+      </c>
+      <c r="G24">
+        <v>32.9</v>
+      </c>
+      <c r="H24">
+        <v>179.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>39.7</v>
+      </c>
+      <c r="K24">
+        <v>-1.52</v>
+      </c>
+      <c r="L24">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M24">
+        <v>1.8036876</v>
+      </c>
+      <c r="N24">
+        <v>39.4163124</v>
+      </c>
+      <c r="O24">
+        <v>13.79570934</v>
+      </c>
+      <c r="P24">
+        <v>25.62060306</v>
+      </c>
+      <c r="Q24">
+        <v>24.10060306</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.3018486148944222</v>
+      </c>
+      <c r="T24">
+        <v>0.9879367040201226</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.35</v>
+      </c>
+      <c r="W24">
+        <v>0.029705</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>22.85318144893827</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2411080385031728</v>
+      </c>
+      <c r="C25">
+        <v>152.6111365441147</v>
+      </c>
+      <c r="D25">
+        <v>160.9731365441147</v>
+      </c>
+      <c r="E25">
+        <v>41.262</v>
+      </c>
+      <c r="F25">
+        <v>41.262</v>
+      </c>
+      <c r="G25">
+        <v>32.9</v>
+      </c>
+      <c r="H25">
+        <v>179.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>39.7</v>
+      </c>
+      <c r="K25">
+        <v>-1.52</v>
+      </c>
+      <c r="L25">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M25">
+        <v>1.8856734</v>
+      </c>
+      <c r="N25">
+        <v>39.3343266</v>
+      </c>
+      <c r="O25">
+        <v>13.76701431</v>
+      </c>
+      <c r="P25">
+        <v>25.56731229</v>
+      </c>
+      <c r="Q25">
+        <v>24.04731229</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.3042544006534712</v>
+      </c>
+      <c r="T25">
+        <v>0.9969721595169226</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.35</v>
+      </c>
+      <c r="W25">
+        <v>0.029705</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>21.85956486420183</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2402390573886963</v>
+      </c>
+      <c r="C26">
+        <v>151.5115530957418</v>
+      </c>
+      <c r="D26">
+        <v>161.6675530957418</v>
+      </c>
+      <c r="E26">
+        <v>43.056</v>
+      </c>
+      <c r="F26">
+        <v>43.056</v>
+      </c>
+      <c r="G26">
+        <v>32.9</v>
+      </c>
+      <c r="H26">
+        <v>179.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>39.7</v>
+      </c>
+      <c r="K26">
+        <v>-1.52</v>
+      </c>
+      <c r="L26">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M26">
+        <v>1.9676592</v>
+      </c>
+      <c r="N26">
+        <v>39.25234080000001</v>
+      </c>
+      <c r="O26">
+        <v>13.73831928</v>
+      </c>
+      <c r="P26">
+        <v>25.51402152000001</v>
+      </c>
+      <c r="Q26">
+        <v>23.99402152000001</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.3067234965640741</v>
+      </c>
+      <c r="T26">
+        <v>1.006245390158375</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.35</v>
+      </c>
+      <c r="W26">
+        <v>0.029705</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>20.94874966152675</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2393700762742199</v>
+      </c>
+      <c r="C27">
+        <v>150.417986844751</v>
+      </c>
+      <c r="D27">
+        <v>162.367986844751</v>
+      </c>
+      <c r="E27">
+        <v>44.85</v>
+      </c>
+      <c r="F27">
+        <v>44.85</v>
+      </c>
+      <c r="G27">
+        <v>32.9</v>
+      </c>
+      <c r="H27">
+        <v>179.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>39.7</v>
+      </c>
+      <c r="K27">
+        <v>-1.52</v>
+      </c>
+      <c r="L27">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M27">
+        <v>2.049645</v>
+      </c>
+      <c r="N27">
+        <v>39.17035500000001</v>
+      </c>
+      <c r="O27">
+        <v>13.70962425</v>
+      </c>
+      <c r="P27">
+        <v>25.46073075</v>
+      </c>
+      <c r="Q27">
+        <v>23.94073075</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.3092584350322932</v>
+      </c>
+      <c r="T27">
+        <v>1.015765906950267</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.35</v>
+      </c>
+      <c r="W27">
+        <v>0.029705</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>20.11079967506568</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2385010951597434</v>
+      </c>
+      <c r="C28">
+        <v>149.3305163410004</v>
+      </c>
+      <c r="D28">
+        <v>163.0745163410004</v>
+      </c>
+      <c r="E28">
+        <v>46.64400000000001</v>
+      </c>
+      <c r="F28">
+        <v>46.64400000000001</v>
+      </c>
+      <c r="G28">
+        <v>32.9</v>
+      </c>
+      <c r="H28">
+        <v>179.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>39.7</v>
+      </c>
+      <c r="K28">
+        <v>-1.52</v>
+      </c>
+      <c r="L28">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M28">
+        <v>2.1316308</v>
+      </c>
+      <c r="N28">
+        <v>39.0883692</v>
+      </c>
+      <c r="O28">
+        <v>13.68092922</v>
+      </c>
+      <c r="P28">
+        <v>25.40743998</v>
+      </c>
+      <c r="Q28">
+        <v>23.88743998</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.3118618853510046</v>
+      </c>
+      <c r="T28">
+        <v>1.025543735006804</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.35</v>
+      </c>
+      <c r="W28">
+        <v>0.029705</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>19.33730737987085</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.237632114045267</v>
+      </c>
+      <c r="C29">
+        <v>148.2492215075332</v>
+      </c>
+      <c r="D29">
+        <v>163.7872215075332</v>
+      </c>
+      <c r="E29">
+        <v>48.438</v>
+      </c>
+      <c r="F29">
+        <v>48.438</v>
+      </c>
+      <c r="G29">
+        <v>32.9</v>
+      </c>
+      <c r="H29">
+        <v>179.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>39.7</v>
+      </c>
+      <c r="K29">
+        <v>-1.52</v>
+      </c>
+      <c r="L29">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M29">
+        <v>2.2136166</v>
+      </c>
+      <c r="N29">
+        <v>39.0063834</v>
+      </c>
+      <c r="O29">
+        <v>13.65223419</v>
+      </c>
+      <c r="P29">
+        <v>25.35414921</v>
+      </c>
+      <c r="Q29">
+        <v>23.83414921</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.3145366630757082</v>
+      </c>
+      <c r="T29">
+        <v>1.03558944876352</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.35</v>
+      </c>
+      <c r="W29">
+        <v>0.029705</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>18.621110810246</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2367631329307905</v>
+      </c>
+      <c r="C30">
+        <v>147.1741836707174</v>
+      </c>
+      <c r="D30">
+        <v>164.5061836707173</v>
+      </c>
+      <c r="E30">
+        <v>50.23200000000001</v>
+      </c>
+      <c r="F30">
+        <v>50.23200000000001</v>
+      </c>
+      <c r="G30">
+        <v>32.9</v>
+      </c>
+      <c r="H30">
+        <v>179.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>39.7</v>
+      </c>
+      <c r="K30">
+        <v>-1.52</v>
+      </c>
+      <c r="L30">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M30">
+        <v>2.2956024</v>
+      </c>
+      <c r="N30">
+        <v>38.92439760000001</v>
+      </c>
+      <c r="O30">
+        <v>13.62353916</v>
+      </c>
+      <c r="P30">
+        <v>25.30085844000001</v>
+      </c>
+      <c r="Q30">
+        <v>23.78085844000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.3172857401816535</v>
+      </c>
+      <c r="T30">
+        <v>1.04591421012459</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.35</v>
+      </c>
+      <c r="W30">
+        <v>0.029705</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>17.9560711384515</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.235894151816314</v>
+      </c>
+      <c r="C31">
+        <v>146.1054855911806</v>
+      </c>
+      <c r="D31">
+        <v>165.2314855911806</v>
+      </c>
+      <c r="E31">
+        <v>52.026</v>
+      </c>
+      <c r="F31">
+        <v>52.026</v>
+      </c>
+      <c r="G31">
+        <v>32.9</v>
+      </c>
+      <c r="H31">
+        <v>179.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>39.7</v>
+      </c>
+      <c r="K31">
+        <v>-1.52</v>
+      </c>
+      <c r="L31">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M31">
+        <v>2.3775882</v>
+      </c>
+      <c r="N31">
+        <v>38.84241180000001</v>
+      </c>
+      <c r="O31">
+        <v>13.59484413</v>
+      </c>
+      <c r="P31">
+        <v>25.24756767000001</v>
+      </c>
+      <c r="Q31">
+        <v>23.72756767000001</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.3201122560793155</v>
+      </c>
+      <c r="T31">
+        <v>1.056529809833858</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.35</v>
+      </c>
+      <c r="W31">
+        <v>0.029705</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>17.33689627160835</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2350251707018376</v>
+      </c>
+      <c r="C32">
+        <v>145.0432114955693</v>
+      </c>
+      <c r="D32">
+        <v>165.9632114955693</v>
+      </c>
+      <c r="E32">
+        <v>53.82</v>
+      </c>
+      <c r="F32">
+        <v>53.82</v>
+      </c>
+      <c r="G32">
+        <v>32.9</v>
+      </c>
+      <c r="H32">
+        <v>179.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>39.7</v>
+      </c>
+      <c r="K32">
+        <v>-1.52</v>
+      </c>
+      <c r="L32">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M32">
+        <v>2.459574</v>
+      </c>
+      <c r="N32">
+        <v>38.760426</v>
+      </c>
+      <c r="O32">
+        <v>13.5661491</v>
+      </c>
+      <c r="P32">
+        <v>25.1942769</v>
+      </c>
+      <c r="Q32">
+        <v>23.6742769</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.3230195295740537</v>
+      </c>
+      <c r="T32">
+        <v>1.067448712391963</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.35</v>
+      </c>
+      <c r="W32">
+        <v>0.029705</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>16.7589997292214</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2341561895873611</v>
+      </c>
+      <c r="C33">
+        <v>143.9874471091535</v>
+      </c>
+      <c r="D33">
+        <v>166.7014471091535</v>
+      </c>
+      <c r="E33">
+        <v>55.614</v>
+      </c>
+      <c r="F33">
+        <v>55.614</v>
+      </c>
+      <c r="G33">
+        <v>32.9</v>
+      </c>
+      <c r="H33">
+        <v>179.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>39.7</v>
+      </c>
+      <c r="K33">
+        <v>-1.52</v>
+      </c>
+      <c r="L33">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M33">
+        <v>2.5415598</v>
+      </c>
+      <c r="N33">
+        <v>38.6784402</v>
+      </c>
+      <c r="O33">
+        <v>13.53745407</v>
+      </c>
+      <c r="P33">
+        <v>25.14098613</v>
+      </c>
+      <c r="Q33">
+        <v>23.62098613</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.3260110718657408</v>
+      </c>
+      <c r="T33">
+        <v>1.078684104879289</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.35</v>
+      </c>
+      <c r="W33">
+        <v>0.029705</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>16.21838683473039</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2332872084728846</v>
+      </c>
+      <c r="C34">
+        <v>142.9382796893073</v>
+      </c>
+      <c r="D34">
+        <v>167.4462796893073</v>
+      </c>
+      <c r="E34">
+        <v>57.408</v>
+      </c>
+      <c r="F34">
+        <v>57.408</v>
+      </c>
+      <c r="G34">
+        <v>32.9</v>
+      </c>
+      <c r="H34">
+        <v>179.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>39.7</v>
+      </c>
+      <c r="K34">
+        <v>-1.52</v>
+      </c>
+      <c r="L34">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M34">
+        <v>2.6235456</v>
+      </c>
+      <c r="N34">
+        <v>38.59645440000001</v>
+      </c>
+      <c r="O34">
+        <v>13.50875904</v>
+      </c>
+      <c r="P34">
+        <v>25.08769536</v>
+      </c>
+      <c r="Q34">
+        <v>23.56769536000001</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.3290906006954186</v>
+      </c>
+      <c r="T34">
+        <v>1.090249950086829</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.35</v>
+      </c>
+      <c r="W34">
+        <v>0.029705</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>15.71156224614506</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2324182273584082</v>
+      </c>
+      <c r="C35">
+        <v>141.8957980598892</v>
+      </c>
+      <c r="D35">
+        <v>168.1977980598892</v>
+      </c>
+      <c r="E35">
+        <v>59.20200000000001</v>
+      </c>
+      <c r="F35">
+        <v>59.20200000000001</v>
+      </c>
+      <c r="G35">
+        <v>32.9</v>
+      </c>
+      <c r="H35">
+        <v>179.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>39.7</v>
+      </c>
+      <c r="K35">
+        <v>-1.52</v>
+      </c>
+      <c r="L35">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M35">
+        <v>2.7055314</v>
+      </c>
+      <c r="N35">
+        <v>38.51446860000001</v>
+      </c>
+      <c r="O35">
+        <v>13.48006401</v>
+      </c>
+      <c r="P35">
+        <v>25.03440459000001</v>
+      </c>
+      <c r="Q35">
+        <v>23.51440459000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.3322620557588182</v>
+      </c>
+      <c r="T35">
+        <v>1.102161044405043</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.35</v>
+      </c>
+      <c r="W35">
+        <v>0.029705</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>15.23545429929218</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2315492462439318</v>
+      </c>
+      <c r="C36">
+        <v>140.8600926465543</v>
+      </c>
+      <c r="D36">
+        <v>168.9560926465543</v>
+      </c>
+      <c r="E36">
+        <v>60.99600000000001</v>
+      </c>
+      <c r="F36">
+        <v>60.99600000000001</v>
+      </c>
+      <c r="G36">
+        <v>32.9</v>
+      </c>
+      <c r="H36">
+        <v>179.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>39.7</v>
+      </c>
+      <c r="K36">
+        <v>-1.52</v>
+      </c>
+      <c r="L36">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M36">
+        <v>2.787517200000001</v>
+      </c>
+      <c r="N36">
+        <v>38.4324828</v>
+      </c>
+      <c r="O36">
+        <v>13.45136898</v>
+      </c>
+      <c r="P36">
+        <v>24.98111382</v>
+      </c>
+      <c r="Q36">
+        <v>23.46111382</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.3355296155211088</v>
+      </c>
+      <c r="T36">
+        <v>1.114433080975324</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.35</v>
+      </c>
+      <c r="W36">
+        <v>0.029705</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>14.78735270225418</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2306802651294553</v>
+      </c>
+      <c r="C37">
+        <v>139.8312555130249</v>
+      </c>
+      <c r="D37">
+        <v>169.7212555130249</v>
+      </c>
+      <c r="E37">
+        <v>62.79000000000001</v>
+      </c>
+      <c r="F37">
+        <v>62.79000000000001</v>
+      </c>
+      <c r="G37">
+        <v>32.9</v>
+      </c>
+      <c r="H37">
+        <v>179.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>39.7</v>
+      </c>
+      <c r="K37">
+        <v>-1.52</v>
+      </c>
+      <c r="L37">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M37">
+        <v>2.869503</v>
+      </c>
+      <c r="N37">
+        <v>38.350497</v>
+      </c>
+      <c r="O37">
+        <v>13.42267395</v>
+      </c>
+      <c r="P37">
+        <v>24.92782305</v>
+      </c>
+      <c r="Q37">
+        <v>23.40782305</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.3388977155837774</v>
+      </c>
+      <c r="T37">
+        <v>1.127082718670844</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.35</v>
+      </c>
+      <c r="W37">
+        <v>0.029705</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>14.3648569107612</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2298112840149789</v>
+      </c>
+      <c r="C38">
+        <v>138.809380398351</v>
+      </c>
+      <c r="D38">
+        <v>170.493380398351</v>
+      </c>
+      <c r="E38">
+        <v>64.584</v>
+      </c>
+      <c r="F38">
+        <v>64.584</v>
+      </c>
+      <c r="G38">
+        <v>32.9</v>
+      </c>
+      <c r="H38">
+        <v>179.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>39.7</v>
+      </c>
+      <c r="K38">
+        <v>-1.52</v>
+      </c>
+      <c r="L38">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M38">
+        <v>2.9514888</v>
+      </c>
+      <c r="N38">
+        <v>38.26851120000001</v>
+      </c>
+      <c r="O38">
+        <v>13.39397892</v>
+      </c>
+      <c r="P38">
+        <v>24.87453228</v>
+      </c>
+      <c r="Q38">
+        <v>23.35453228</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.3423710687734045</v>
+      </c>
+      <c r="T38">
+        <v>1.140127657544349</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.35</v>
+      </c>
+      <c r="W38">
+        <v>0.029705</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>13.9658331076845</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2289423029005024</v>
+      </c>
+      <c r="C39">
+        <v>137.7945627551932</v>
+      </c>
+      <c r="D39">
+        <v>171.2725627551932</v>
+      </c>
+      <c r="E39">
+        <v>66.378</v>
+      </c>
+      <c r="F39">
+        <v>66.378</v>
+      </c>
+      <c r="G39">
+        <v>32.9</v>
+      </c>
+      <c r="H39">
+        <v>179.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>39.7</v>
+      </c>
+      <c r="K39">
+        <v>-1.52</v>
+      </c>
+      <c r="L39">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M39">
+        <v>3.0334746</v>
+      </c>
+      <c r="N39">
+        <v>38.18652540000001</v>
+      </c>
+      <c r="O39">
+        <v>13.36528389</v>
+      </c>
+      <c r="P39">
+        <v>24.82124151000001</v>
+      </c>
+      <c r="Q39">
+        <v>23.30124151000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.3459546871436546</v>
+      </c>
+      <c r="T39">
+        <v>1.153586721461458</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.35</v>
+      </c>
+      <c r="W39">
+        <v>0.029705</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>13.58837815882817</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2280733217860259</v>
+      </c>
+      <c r="C40">
+        <v>136.7868997891599</v>
+      </c>
+      <c r="D40">
+        <v>172.0588997891599</v>
+      </c>
+      <c r="E40">
+        <v>68.172</v>
+      </c>
+      <c r="F40">
+        <v>68.172</v>
+      </c>
+      <c r="G40">
+        <v>32.9</v>
+      </c>
+      <c r="H40">
+        <v>179.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>39.7</v>
+      </c>
+      <c r="K40">
+        <v>-1.52</v>
+      </c>
+      <c r="L40">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M40">
+        <v>3.1154604</v>
+      </c>
+      <c r="N40">
+        <v>38.1045396</v>
+      </c>
+      <c r="O40">
+        <v>13.33658886</v>
+      </c>
+      <c r="P40">
+        <v>24.76795074</v>
+      </c>
+      <c r="Q40">
+        <v>23.24795074</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.3496539061064934</v>
+      </c>
+      <c r="T40">
+        <v>1.167479948730731</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.35</v>
+      </c>
+      <c r="W40">
+        <v>0.029705</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>13.23078925991163</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2276099406715494</v>
+      </c>
+      <c r="C41">
+        <v>135.4151701656895</v>
+      </c>
+      <c r="D41">
+        <v>172.4811701656895</v>
+      </c>
+      <c r="E41">
+        <v>69.96600000000001</v>
+      </c>
+      <c r="F41">
+        <v>69.96600000000001</v>
+      </c>
+      <c r="G41">
+        <v>32.9</v>
+      </c>
+      <c r="H41">
+        <v>179.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>39.7</v>
+      </c>
+      <c r="K41">
+        <v>-1.52</v>
+      </c>
+      <c r="L41">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M41">
+        <v>3.309391800000001</v>
+      </c>
+      <c r="N41">
+        <v>37.91060820000001</v>
+      </c>
+      <c r="O41">
+        <v>13.26871287</v>
+      </c>
+      <c r="P41">
+        <v>24.64189533</v>
+      </c>
+      <c r="Q41">
+        <v>23.12189533</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.3534744109369663</v>
+      </c>
+      <c r="T41">
+        <v>1.181828691648177</v>
+      </c>
+      <c r="U41">
+        <v>0.0473</v>
+      </c>
+      <c r="V41">
+        <v>0.35</v>
+      </c>
+      <c r="W41">
+        <v>0.030745</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>12.45546084933189</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.226751359557073</v>
+      </c>
+      <c r="C42">
+        <v>134.4090818661211</v>
+      </c>
+      <c r="D42">
+        <v>173.2690818661211</v>
+      </c>
+      <c r="E42">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="F42">
+        <v>71.76000000000001</v>
+      </c>
+      <c r="G42">
+        <v>32.9</v>
+      </c>
+      <c r="H42">
+        <v>179.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>39.7</v>
+      </c>
+      <c r="K42">
+        <v>-1.52</v>
+      </c>
+      <c r="L42">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M42">
+        <v>3.394248</v>
+      </c>
+      <c r="N42">
+        <v>37.82575200000001</v>
+      </c>
+      <c r="O42">
+        <v>13.2390132</v>
+      </c>
+      <c r="P42">
+        <v>24.58673880000001</v>
+      </c>
+      <c r="Q42">
+        <v>23.06673880000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.357422265928455</v>
+      </c>
+      <c r="T42">
+        <v>1.196655725996205</v>
+      </c>
+      <c r="U42">
+        <v>0.0473</v>
+      </c>
+      <c r="V42">
+        <v>0.35</v>
+      </c>
+      <c r="W42">
+        <v>0.030745</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>12.1440743280986</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2258927784425965</v>
+      </c>
+      <c r="C43">
+        <v>133.410225124195</v>
+      </c>
+      <c r="D43">
+        <v>174.064225124195</v>
+      </c>
+      <c r="E43">
+        <v>73.554</v>
+      </c>
+      <c r="F43">
+        <v>73.554</v>
+      </c>
+      <c r="G43">
+        <v>32.9</v>
+      </c>
+      <c r="H43">
+        <v>179.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>39.7</v>
+      </c>
+      <c r="K43">
+        <v>-1.52</v>
+      </c>
+      <c r="L43">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M43">
+        <v>3.4791042</v>
+      </c>
+      <c r="N43">
+        <v>37.7408958</v>
+      </c>
+      <c r="O43">
+        <v>13.20931353</v>
+      </c>
+      <c r="P43">
+        <v>24.53158227</v>
+      </c>
+      <c r="Q43">
+        <v>23.01158227</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.3615039465128755</v>
+      </c>
+      <c r="T43">
+        <v>1.211985371678064</v>
+      </c>
+      <c r="U43">
+        <v>0.0473</v>
+      </c>
+      <c r="V43">
+        <v>0.35</v>
+      </c>
+      <c r="W43">
+        <v>0.030745</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>11.84787739326692</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2250341973281201</v>
+      </c>
+      <c r="C44">
+        <v>132.4186999571833</v>
+      </c>
+      <c r="D44">
+        <v>174.8666999571833</v>
+      </c>
+      <c r="E44">
+        <v>75.348</v>
+      </c>
+      <c r="F44">
+        <v>75.348</v>
+      </c>
+      <c r="G44">
+        <v>32.9</v>
+      </c>
+      <c r="H44">
+        <v>179.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>39.7</v>
+      </c>
+      <c r="K44">
+        <v>-1.52</v>
+      </c>
+      <c r="L44">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M44">
+        <v>3.5639604</v>
+      </c>
+      <c r="N44">
+        <v>37.65603960000001</v>
+      </c>
+      <c r="O44">
+        <v>13.17961386</v>
+      </c>
+      <c r="P44">
+        <v>24.47642574</v>
+      </c>
+      <c r="Q44">
+        <v>22.95642574</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.3657263747036553</v>
+      </c>
+      <c r="T44">
+        <v>1.227843625831711</v>
+      </c>
+      <c r="U44">
+        <v>0.0473</v>
+      </c>
+      <c r="V44">
+        <v>0.35</v>
+      </c>
+      <c r="W44">
+        <v>0.030745</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>11.56578507437962</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2241756162136436</v>
+      </c>
+      <c r="C45">
+        <v>131.4346082353089</v>
+      </c>
+      <c r="D45">
+        <v>175.6766082353089</v>
+      </c>
+      <c r="E45">
+        <v>77.142</v>
+      </c>
+      <c r="F45">
+        <v>77.142</v>
+      </c>
+      <c r="G45">
+        <v>32.9</v>
+      </c>
+      <c r="H45">
+        <v>179.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>39.7</v>
+      </c>
+      <c r="K45">
+        <v>-1.52</v>
+      </c>
+      <c r="L45">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M45">
+        <v>3.6488166</v>
+      </c>
+      <c r="N45">
+        <v>37.57118340000001</v>
+      </c>
+      <c r="O45">
+        <v>13.14991419</v>
+      </c>
+      <c r="P45">
+        <v>24.42126921000001</v>
+      </c>
+      <c r="Q45">
+        <v>22.90126921000001</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.3700969582695502</v>
+      </c>
+      <c r="T45">
+        <v>1.244258309955662</v>
+      </c>
+      <c r="U45">
+        <v>0.0473</v>
+      </c>
+      <c r="V45">
+        <v>0.35</v>
+      </c>
+      <c r="W45">
+        <v>0.030745</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>11.29681332846381</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2233170350991672</v>
+      </c>
+      <c r="C46">
+        <v>130.4580537248544</v>
+      </c>
+      <c r="D46">
+        <v>176.4940537248544</v>
+      </c>
+      <c r="E46">
+        <v>78.93600000000001</v>
+      </c>
+      <c r="F46">
+        <v>78.93600000000001</v>
+      </c>
+      <c r="G46">
+        <v>32.9</v>
+      </c>
+      <c r="H46">
+        <v>179.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>39.7</v>
+      </c>
+      <c r="K46">
+        <v>-1.52</v>
+      </c>
+      <c r="L46">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M46">
+        <v>3.7336728</v>
+      </c>
+      <c r="N46">
+        <v>37.48632720000001</v>
+      </c>
+      <c r="O46">
+        <v>13.12021452</v>
+      </c>
+      <c r="P46">
+        <v>24.36611268</v>
+      </c>
+      <c r="Q46">
+        <v>22.84611268</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.3746236341056556</v>
+      </c>
+      <c r="T46">
+        <v>1.261259232798325</v>
+      </c>
+      <c r="U46">
+        <v>0.0473</v>
+      </c>
+      <c r="V46">
+        <v>0.35</v>
+      </c>
+      <c r="W46">
+        <v>0.030745</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>11.04006757099872</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2224584539846907</v>
+      </c>
+      <c r="C47">
+        <v>129.4891421324818</v>
+      </c>
+      <c r="D47">
+        <v>177.3191421324819</v>
+      </c>
+      <c r="E47">
+        <v>80.73</v>
+      </c>
+      <c r="F47">
+        <v>80.73</v>
+      </c>
+      <c r="G47">
+        <v>32.9</v>
+      </c>
+      <c r="H47">
+        <v>179.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>39.7</v>
+      </c>
+      <c r="K47">
+        <v>-1.52</v>
+      </c>
+      <c r="L47">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M47">
+        <v>3.818529</v>
+      </c>
+      <c r="N47">
+        <v>37.40147100000001</v>
+      </c>
+      <c r="O47">
+        <v>13.09051485</v>
+      </c>
+      <c r="P47">
+        <v>24.31095615000001</v>
+      </c>
+      <c r="Q47">
+        <v>22.79095615000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.3793149163358012</v>
+      </c>
+      <c r="T47">
+        <v>1.278878371017085</v>
+      </c>
+      <c r="U47">
+        <v>0.0473</v>
+      </c>
+      <c r="V47">
+        <v>0.35</v>
+      </c>
+      <c r="W47">
+        <v>0.030745</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>10.79473273608764</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2215998728702143</v>
+      </c>
+      <c r="C48">
+        <v>128.5279811508011</v>
+      </c>
+      <c r="D48">
+        <v>178.1519811508011</v>
+      </c>
+      <c r="E48">
+        <v>82.524</v>
+      </c>
+      <c r="F48">
+        <v>82.524</v>
+      </c>
+      <c r="G48">
+        <v>32.9</v>
+      </c>
+      <c r="H48">
+        <v>179.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>39.7</v>
+      </c>
+      <c r="K48">
+        <v>-1.52</v>
+      </c>
+      <c r="L48">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M48">
+        <v>3.9033852</v>
+      </c>
+      <c r="N48">
+        <v>37.3166148</v>
+      </c>
+      <c r="O48">
+        <v>13.06081518</v>
+      </c>
+      <c r="P48">
+        <v>24.25579962</v>
+      </c>
+      <c r="Q48">
+        <v>22.73579962000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.384179949759656</v>
+      </c>
+      <c r="T48">
+        <v>1.297150069910615</v>
+      </c>
+      <c r="U48">
+        <v>0.0473</v>
+      </c>
+      <c r="V48">
+        <v>0.35</v>
+      </c>
+      <c r="W48">
+        <v>0.030745</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>10.56006463312921</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2207412917557378</v>
+      </c>
+      <c r="C49">
+        <v>127.5746805052281</v>
+      </c>
+      <c r="D49">
+        <v>178.9926805052281</v>
+      </c>
+      <c r="E49">
+        <v>84.31800000000001</v>
+      </c>
+      <c r="F49">
+        <v>84.31800000000001</v>
+      </c>
+      <c r="G49">
+        <v>32.9</v>
+      </c>
+      <c r="H49">
+        <v>179.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>39.7</v>
+      </c>
+      <c r="K49">
+        <v>-1.52</v>
+      </c>
+      <c r="L49">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M49">
+        <v>3.988241400000001</v>
+      </c>
+      <c r="N49">
+        <v>37.23175860000001</v>
+      </c>
+      <c r="O49">
+        <v>13.03111551</v>
+      </c>
+      <c r="P49">
+        <v>24.20064309000001</v>
+      </c>
+      <c r="Q49">
+        <v>22.68064309000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.3892285693504486</v>
+      </c>
+      <c r="T49">
+        <v>1.316111266875598</v>
+      </c>
+      <c r="U49">
+        <v>0.0473</v>
+      </c>
+      <c r="V49">
+        <v>0.35</v>
+      </c>
+      <c r="W49">
+        <v>0.030745</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>10.33538240689242</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2210683106412613</v>
+      </c>
+      <c r="C50">
+        <v>125.4595386309782</v>
+      </c>
+      <c r="D50">
+        <v>178.6715386309782</v>
+      </c>
+      <c r="E50">
+        <v>86.11199999999999</v>
+      </c>
+      <c r="F50">
+        <v>86.11199999999999</v>
+      </c>
+      <c r="G50">
+        <v>32.9</v>
+      </c>
+      <c r="H50">
+        <v>179.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>39.7</v>
+      </c>
+      <c r="K50">
+        <v>-1.52</v>
+      </c>
+      <c r="L50">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M50">
+        <v>4.4003232</v>
+      </c>
+      <c r="N50">
+        <v>36.8196768</v>
+      </c>
+      <c r="O50">
+        <v>12.88688688</v>
+      </c>
+      <c r="P50">
+        <v>23.93278992</v>
+      </c>
+      <c r="Q50">
+        <v>22.41278992000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.3944713666178102</v>
+      </c>
+      <c r="T50">
+        <v>1.335801740646926</v>
+      </c>
+      <c r="U50">
+        <v>0.0511</v>
+      </c>
+      <c r="V50">
+        <v>0.35</v>
+      </c>
+      <c r="W50">
+        <v>0.033215</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>9.367493733187599</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2202344295267848</v>
+      </c>
+      <c r="C51">
+        <v>124.486721369819</v>
+      </c>
+      <c r="D51">
+        <v>179.492721369819</v>
+      </c>
+      <c r="E51">
+        <v>87.90600000000001</v>
+      </c>
+      <c r="F51">
+        <v>87.90600000000001</v>
+      </c>
+      <c r="G51">
+        <v>32.9</v>
+      </c>
+      <c r="H51">
+        <v>179.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>39.7</v>
+      </c>
+      <c r="K51">
+        <v>-1.52</v>
+      </c>
+      <c r="L51">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M51">
+        <v>4.4919966</v>
+      </c>
+      <c r="N51">
+        <v>36.72800340000001</v>
+      </c>
+      <c r="O51">
+        <v>12.85480119</v>
+      </c>
+      <c r="P51">
+        <v>23.87320221</v>
+      </c>
+      <c r="Q51">
+        <v>22.35320221</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.3999197637780095</v>
+      </c>
+      <c r="T51">
+        <v>1.356264389860268</v>
+      </c>
+      <c r="U51">
+        <v>0.0511</v>
+      </c>
+      <c r="V51">
+        <v>0.35</v>
+      </c>
+      <c r="W51">
+        <v>0.033215</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>9.176320391693976</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2194005484123084</v>
+      </c>
+      <c r="C52">
+        <v>123.5214873500561</v>
+      </c>
+      <c r="D52">
+        <v>180.3214873500561</v>
+      </c>
+      <c r="E52">
+        <v>89.7</v>
+      </c>
+      <c r="F52">
+        <v>89.7</v>
+      </c>
+      <c r="G52">
+        <v>32.9</v>
+      </c>
+      <c r="H52">
+        <v>179.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>39.7</v>
+      </c>
+      <c r="K52">
+        <v>-1.52</v>
+      </c>
+      <c r="L52">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M52">
+        <v>4.58367</v>
+      </c>
+      <c r="N52">
+        <v>36.63633000000001</v>
+      </c>
+      <c r="O52">
+        <v>12.8227155</v>
+      </c>
+      <c r="P52">
+        <v>23.81361450000001</v>
+      </c>
+      <c r="Q52">
+        <v>22.29361450000001</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.4055860968246168</v>
+      </c>
+      <c r="T52">
+        <v>1.377545545042143</v>
+      </c>
+      <c r="U52">
+        <v>0.0511</v>
+      </c>
+      <c r="V52">
+        <v>0.35</v>
+      </c>
+      <c r="W52">
+        <v>0.033215</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>8.992793983860096</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2185666672978319</v>
+      </c>
+      <c r="C53">
+        <v>122.5639421005154</v>
+      </c>
+      <c r="D53">
+        <v>181.1579421005154</v>
+      </c>
+      <c r="E53">
+        <v>91.494</v>
+      </c>
+      <c r="F53">
+        <v>91.494</v>
+      </c>
+      <c r="G53">
+        <v>32.9</v>
+      </c>
+      <c r="H53">
+        <v>179.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>39.7</v>
+      </c>
+      <c r="K53">
+        <v>-1.52</v>
+      </c>
+      <c r="L53">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M53">
+        <v>4.6753434</v>
+      </c>
+      <c r="N53">
+        <v>36.5446566</v>
+      </c>
+      <c r="O53">
+        <v>12.79062981</v>
+      </c>
+      <c r="P53">
+        <v>23.75402679</v>
+      </c>
+      <c r="Q53">
+        <v>22.23402679000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.4114837087710856</v>
+      </c>
+      <c r="T53">
+        <v>1.39969531880287</v>
+      </c>
+      <c r="U53">
+        <v>0.0511</v>
+      </c>
+      <c r="V53">
+        <v>0.35</v>
+      </c>
+      <c r="W53">
+        <v>0.033215</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>8.816464690058917</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2177327861833555</v>
+      </c>
+      <c r="C54">
+        <v>121.6141931172085</v>
+      </c>
+      <c r="D54">
+        <v>182.0021931172085</v>
+      </c>
+      <c r="E54">
+        <v>93.28800000000001</v>
+      </c>
+      <c r="F54">
+        <v>93.28800000000001</v>
+      </c>
+      <c r="G54">
+        <v>32.9</v>
+      </c>
+      <c r="H54">
+        <v>179.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>39.7</v>
+      </c>
+      <c r="K54">
+        <v>-1.52</v>
+      </c>
+      <c r="L54">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M54">
+        <v>4.7670168</v>
+      </c>
+      <c r="N54">
+        <v>36.45298320000001</v>
+      </c>
+      <c r="O54">
+        <v>12.75854412</v>
+      </c>
+      <c r="P54">
+        <v>23.69443908</v>
+      </c>
+      <c r="Q54">
+        <v>22.17443908</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.4176270545486573</v>
+      </c>
+      <c r="T54">
+        <v>1.422767999803627</v>
+      </c>
+      <c r="U54">
+        <v>0.0511</v>
+      </c>
+      <c r="V54">
+        <v>0.35</v>
+      </c>
+      <c r="W54">
+        <v>0.033215</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>8.646917292173168</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.216898905068879</v>
+      </c>
+      <c r="C55">
+        <v>120.6723499093856</v>
+      </c>
+      <c r="D55">
+        <v>182.8543499093856</v>
+      </c>
+      <c r="E55">
+        <v>95.08200000000001</v>
+      </c>
+      <c r="F55">
+        <v>95.08200000000001</v>
+      </c>
+      <c r="G55">
+        <v>32.9</v>
+      </c>
+      <c r="H55">
+        <v>179.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>39.7</v>
+      </c>
+      <c r="K55">
+        <v>-1.52</v>
+      </c>
+      <c r="L55">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M55">
+        <v>4.858690200000001</v>
+      </c>
+      <c r="N55">
+        <v>36.36130980000001</v>
+      </c>
+      <c r="O55">
+        <v>12.72645843</v>
+      </c>
+      <c r="P55">
+        <v>23.63485137000001</v>
+      </c>
+      <c r="Q55">
+        <v>22.11485137000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.4240318192954873</v>
+      </c>
+      <c r="T55">
+        <v>1.446822497017183</v>
+      </c>
+      <c r="U55">
+        <v>0.0511</v>
+      </c>
+      <c r="V55">
+        <v>0.35</v>
+      </c>
+      <c r="W55">
+        <v>0.033215</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>8.483767909301976</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2160650239544026</v>
+      </c>
+      <c r="C56">
+        <v>119.7385240468879</v>
+      </c>
+      <c r="D56">
+        <v>183.7145240468879</v>
+      </c>
+      <c r="E56">
+        <v>96.876</v>
+      </c>
+      <c r="F56">
+        <v>96.876</v>
+      </c>
+      <c r="G56">
+        <v>32.9</v>
+      </c>
+      <c r="H56">
+        <v>179.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>39.7</v>
+      </c>
+      <c r="K56">
+        <v>-1.52</v>
+      </c>
+      <c r="L56">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M56">
+        <v>4.9503636</v>
+      </c>
+      <c r="N56">
+        <v>36.2696364</v>
+      </c>
+      <c r="O56">
+        <v>12.69437274</v>
+      </c>
+      <c r="P56">
+        <v>23.57526366</v>
+      </c>
+      <c r="Q56">
+        <v>22.05526366</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.4307150520747882</v>
+      </c>
+      <c r="T56">
+        <v>1.471922841935676</v>
+      </c>
+      <c r="U56">
+        <v>0.0511</v>
+      </c>
+      <c r="V56">
+        <v>0.35</v>
+      </c>
+      <c r="W56">
+        <v>0.033215</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>8.326661096166754</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2152311428399261</v>
+      </c>
+      <c r="C57">
+        <v>118.812829208844</v>
+      </c>
+      <c r="D57">
+        <v>184.582829208844</v>
+      </c>
+      <c r="E57">
+        <v>98.67000000000002</v>
+      </c>
+      <c r="F57">
+        <v>98.67000000000002</v>
+      </c>
+      <c r="G57">
+        <v>32.9</v>
+      </c>
+      <c r="H57">
+        <v>179.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>39.7</v>
+      </c>
+      <c r="K57">
+        <v>-1.52</v>
+      </c>
+      <c r="L57">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M57">
+        <v>5.042037000000001</v>
+      </c>
+      <c r="N57">
+        <v>36.17796300000001</v>
+      </c>
+      <c r="O57">
+        <v>12.66228705</v>
+      </c>
+      <c r="P57">
+        <v>23.51567595</v>
+      </c>
+      <c r="Q57">
+        <v>21.99567595</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.4376953174220581</v>
+      </c>
+      <c r="T57">
+        <v>1.498138757739435</v>
+      </c>
+      <c r="U57">
+        <v>0.0511</v>
+      </c>
+      <c r="V57">
+        <v>0.35</v>
+      </c>
+      <c r="W57">
+        <v>0.033215</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>8.175267258054632</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2143972617254496</v>
+      </c>
+      <c r="C58">
+        <v>117.8953812337529</v>
+      </c>
+      <c r="D58">
+        <v>185.4593812337529</v>
+      </c>
+      <c r="E58">
+        <v>100.464</v>
+      </c>
+      <c r="F58">
+        <v>100.464</v>
+      </c>
+      <c r="G58">
+        <v>32.9</v>
+      </c>
+      <c r="H58">
+        <v>179.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>39.7</v>
+      </c>
+      <c r="K58">
+        <v>-1.52</v>
+      </c>
+      <c r="L58">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M58">
+        <v>5.133710400000001</v>
+      </c>
+      <c r="N58">
+        <v>36.08628960000001</v>
+      </c>
+      <c r="O58">
+        <v>12.63020136</v>
+      </c>
+      <c r="P58">
+        <v>23.45608824000001</v>
+      </c>
+      <c r="Q58">
+        <v>21.93608824000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.4449928675578401</v>
+      </c>
+      <c r="T58">
+        <v>1.525546306079728</v>
+      </c>
+      <c r="U58">
+        <v>0.0511</v>
+      </c>
+      <c r="V58">
+        <v>0.35</v>
+      </c>
+      <c r="W58">
+        <v>0.033215</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>8.029280342732228</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2135633806109731</v>
+      </c>
+      <c r="C59">
+        <v>116.9862981710006</v>
+      </c>
+      <c r="D59">
+        <v>186.3442981710006</v>
+      </c>
+      <c r="E59">
+        <v>102.258</v>
+      </c>
+      <c r="F59">
+        <v>102.258</v>
+      </c>
+      <c r="G59">
+        <v>32.9</v>
+      </c>
+      <c r="H59">
+        <v>179.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>39.7</v>
+      </c>
+      <c r="K59">
+        <v>-1.52</v>
+      </c>
+      <c r="L59">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M59">
+        <v>5.2253838</v>
+      </c>
+      <c r="N59">
+        <v>35.9946162</v>
+      </c>
+      <c r="O59">
+        <v>12.59811567</v>
+      </c>
+      <c r="P59">
+        <v>23.39650053</v>
+      </c>
+      <c r="Q59">
+        <v>21.87650053</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.4526298386301701</v>
+      </c>
+      <c r="T59">
+        <v>1.554228624110268</v>
+      </c>
+      <c r="U59">
+        <v>0.0511</v>
+      </c>
+      <c r="V59">
+        <v>0.35</v>
+      </c>
+      <c r="W59">
+        <v>0.033215</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>7.888415775315873</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2134457994964967</v>
+      </c>
+      <c r="C60">
+        <v>115.3177553553042</v>
+      </c>
+      <c r="D60">
+        <v>186.4697553553042</v>
+      </c>
+      <c r="E60">
+        <v>104.052</v>
+      </c>
+      <c r="F60">
+        <v>104.052</v>
+      </c>
+      <c r="G60">
+        <v>32.9</v>
+      </c>
+      <c r="H60">
+        <v>179.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>39.7</v>
+      </c>
+      <c r="K60">
+        <v>-1.52</v>
+      </c>
+      <c r="L60">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M60">
+        <v>5.514756</v>
+      </c>
+      <c r="N60">
+        <v>35.70524400000001</v>
+      </c>
+      <c r="O60">
+        <v>12.4968354</v>
+      </c>
+      <c r="P60">
+        <v>23.20840860000001</v>
+      </c>
+      <c r="Q60">
+        <v>21.68840860000001</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.4606304749916588</v>
+      </c>
+      <c r="T60">
+        <v>1.584276766808929</v>
+      </c>
+      <c r="U60">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V60">
+        <v>0.35</v>
+      </c>
+      <c r="W60">
+        <v>0.03445</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>7.474492071816052</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2126242683820202</v>
+      </c>
+      <c r="C61">
+        <v>114.405051778175</v>
+      </c>
+      <c r="D61">
+        <v>187.351051778175</v>
+      </c>
+      <c r="E61">
+        <v>105.846</v>
+      </c>
+      <c r="F61">
+        <v>105.846</v>
+      </c>
+      <c r="G61">
+        <v>32.9</v>
+      </c>
+      <c r="H61">
+        <v>179.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>39.7</v>
+      </c>
+      <c r="K61">
+        <v>-1.52</v>
+      </c>
+      <c r="L61">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M61">
+        <v>5.609838000000001</v>
+      </c>
+      <c r="N61">
+        <v>35.610162</v>
+      </c>
+      <c r="O61">
+        <v>12.4635567</v>
+      </c>
+      <c r="P61">
+        <v>23.1466053</v>
+      </c>
+      <c r="Q61">
+        <v>21.6266053</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.4690213862976103</v>
+      </c>
+      <c r="T61">
+        <v>1.615790672566061</v>
+      </c>
+      <c r="U61">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V61">
+        <v>0.35</v>
+      </c>
+      <c r="W61">
+        <v>0.03445</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>7.347805765514084</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2118027372675438</v>
+      </c>
+      <c r="C62">
+        <v>113.5007181545378</v>
+      </c>
+      <c r="D62">
+        <v>188.2407181545377</v>
+      </c>
+      <c r="E62">
+        <v>107.64</v>
+      </c>
+      <c r="F62">
+        <v>107.64</v>
+      </c>
+      <c r="G62">
+        <v>32.9</v>
+      </c>
+      <c r="H62">
+        <v>179.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>39.7</v>
+      </c>
+      <c r="K62">
+        <v>-1.52</v>
+      </c>
+      <c r="L62">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M62">
+        <v>5.70492</v>
+      </c>
+      <c r="N62">
+        <v>35.51508</v>
+      </c>
+      <c r="O62">
+        <v>12.430278</v>
+      </c>
+      <c r="P62">
+        <v>23.084802</v>
+      </c>
+      <c r="Q62">
+        <v>21.564802</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.4778318431688595</v>
+      </c>
+      <c r="T62">
+        <v>1.648880273611049</v>
+      </c>
+      <c r="U62">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V62">
+        <v>0.35</v>
+      </c>
+      <c r="W62">
+        <v>0.03445</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>7.22534233608885</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2109812061530673</v>
+      </c>
+      <c r="C63">
+        <v>112.6048742914965</v>
+      </c>
+      <c r="D63">
+        <v>189.1388742914965</v>
+      </c>
+      <c r="E63">
+        <v>109.434</v>
+      </c>
+      <c r="F63">
+        <v>109.434</v>
+      </c>
+      <c r="G63">
+        <v>32.9</v>
+      </c>
+      <c r="H63">
+        <v>179.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>39.7</v>
+      </c>
+      <c r="K63">
+        <v>-1.52</v>
+      </c>
+      <c r="L63">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M63">
+        <v>5.800002</v>
+      </c>
+      <c r="N63">
+        <v>35.41999800000001</v>
+      </c>
+      <c r="O63">
+        <v>12.3969993</v>
+      </c>
+      <c r="P63">
+        <v>23.02299870000001</v>
+      </c>
+      <c r="Q63">
+        <v>21.50299870000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.4870941183411983</v>
+      </c>
+      <c r="T63">
+        <v>1.68366677727373</v>
+      </c>
+      <c r="U63">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V63">
+        <v>0.35</v>
+      </c>
+      <c r="W63">
+        <v>0.03445</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>7.106894101071001</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2101596750385909</v>
+      </c>
+      <c r="C64">
+        <v>111.7176422936681</v>
+      </c>
+      <c r="D64">
+        <v>190.0456422936681</v>
+      </c>
+      <c r="E64">
+        <v>111.228</v>
+      </c>
+      <c r="F64">
+        <v>111.228</v>
+      </c>
+      <c r="G64">
+        <v>32.9</v>
+      </c>
+      <c r="H64">
+        <v>179.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>39.7</v>
+      </c>
+      <c r="K64">
+        <v>-1.52</v>
+      </c>
+      <c r="L64">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M64">
+        <v>5.895084000000001</v>
+      </c>
+      <c r="N64">
+        <v>35.324916</v>
+      </c>
+      <c r="O64">
+        <v>12.3637206</v>
+      </c>
+      <c r="P64">
+        <v>22.9611954</v>
+      </c>
+      <c r="Q64">
+        <v>21.4411954</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.4968438816805024</v>
+      </c>
+      <c r="T64">
+        <v>1.720284149550236</v>
+      </c>
+      <c r="U64">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V64">
+        <v>0.35</v>
+      </c>
+      <c r="W64">
+        <v>0.03445</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>6.992266776860177</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2093381439241144</v>
+      </c>
+      <c r="C65">
+        <v>110.839146618521</v>
+      </c>
+      <c r="D65">
+        <v>190.961146618521</v>
+      </c>
+      <c r="E65">
+        <v>113.022</v>
+      </c>
+      <c r="F65">
+        <v>113.022</v>
+      </c>
+      <c r="G65">
+        <v>32.9</v>
+      </c>
+      <c r="H65">
+        <v>179.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>39.7</v>
+      </c>
+      <c r="K65">
+        <v>-1.52</v>
+      </c>
+      <c r="L65">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M65">
+        <v>5.990166000000001</v>
+      </c>
+      <c r="N65">
+        <v>35.229834</v>
+      </c>
+      <c r="O65">
+        <v>12.3304419</v>
+      </c>
+      <c r="P65">
+        <v>22.8993921</v>
+      </c>
+      <c r="Q65">
+        <v>21.3793921</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.5071206592543632</v>
+      </c>
+      <c r="T65">
+        <v>1.758880839247093</v>
+      </c>
+      <c r="U65">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V65">
+        <v>0.35</v>
+      </c>
+      <c r="W65">
+        <v>0.03445</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>6.881278415322713</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.208516612809638</v>
+      </c>
+      <c r="C66">
+        <v>109.9695141333215</v>
+      </c>
+      <c r="D66">
+        <v>191.8855141333215</v>
+      </c>
+      <c r="E66">
+        <v>114.816</v>
+      </c>
+      <c r="F66">
+        <v>114.816</v>
+      </c>
+      <c r="G66">
+        <v>32.9</v>
+      </c>
+      <c r="H66">
+        <v>179.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>39.7</v>
+      </c>
+      <c r="K66">
+        <v>-1.52</v>
+      </c>
+      <c r="L66">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M66">
+        <v>6.085248000000001</v>
+      </c>
+      <c r="N66">
+        <v>35.13475200000001</v>
+      </c>
+      <c r="O66">
+        <v>12.2971632</v>
+      </c>
+      <c r="P66">
+        <v>22.83758880000001</v>
+      </c>
+      <c r="Q66">
+        <v>21.31758880000001</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.5179683689156611</v>
+      </c>
+      <c r="T66">
+        <v>1.799621789482665</v>
+      </c>
+      <c r="U66">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V66">
+        <v>0.35</v>
+      </c>
+      <c r="W66">
+        <v>0.03445</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>6.773758440083297</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2076950816951615</v>
+      </c>
+      <c r="C67">
+        <v>109.1088741737422</v>
+      </c>
+      <c r="D67">
+        <v>192.8188741737422</v>
+      </c>
+      <c r="E67">
+        <v>116.61</v>
+      </c>
+      <c r="F67">
+        <v>116.61</v>
+      </c>
+      <c r="G67">
+        <v>32.9</v>
+      </c>
+      <c r="H67">
+        <v>179.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>39.7</v>
+      </c>
+      <c r="K67">
+        <v>-1.52</v>
+      </c>
+      <c r="L67">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M67">
+        <v>6.180330000000001</v>
+      </c>
+      <c r="N67">
+        <v>35.03967</v>
+      </c>
+      <c r="O67">
+        <v>12.2638845</v>
+      </c>
+      <c r="P67">
+        <v>22.7757855</v>
+      </c>
+      <c r="Q67">
+        <v>21.2557855</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.5294359477004614</v>
+      </c>
+      <c r="T67">
+        <v>1.842690794017412</v>
+      </c>
+      <c r="U67">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.35</v>
+      </c>
+      <c r="W67">
+        <v>0.03445</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>6.669546771774321</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.206873550580685</v>
+      </c>
+      <c r="C68">
+        <v>108.257358604188</v>
+      </c>
+      <c r="D68">
+        <v>193.761358604188</v>
+      </c>
+      <c r="E68">
+        <v>118.404</v>
+      </c>
+      <c r="F68">
+        <v>118.404</v>
+      </c>
+      <c r="G68">
+        <v>32.9</v>
+      </c>
+      <c r="H68">
+        <v>179.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>39.7</v>
+      </c>
+      <c r="K68">
+        <v>-1.52</v>
+      </c>
+      <c r="L68">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M68">
+        <v>6.275412000000001</v>
+      </c>
+      <c r="N68">
+        <v>34.944588</v>
+      </c>
+      <c r="O68">
+        <v>12.2306058</v>
+      </c>
+      <c r="P68">
+        <v>22.7139822</v>
+      </c>
+      <c r="Q68">
+        <v>21.1939822</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.5415780899431912</v>
+      </c>
+      <c r="T68">
+        <v>1.888293269407144</v>
+      </c>
+      <c r="U68">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.35</v>
+      </c>
+      <c r="W68">
+        <v>0.03445</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>6.568493032808044</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2060520194662086</v>
+      </c>
+      <c r="C69">
+        <v>107.4151018799021</v>
+      </c>
+      <c r="D69">
+        <v>194.7131018799021</v>
+      </c>
+      <c r="E69">
+        <v>120.198</v>
+      </c>
+      <c r="F69">
+        <v>120.198</v>
+      </c>
+      <c r="G69">
+        <v>32.9</v>
+      </c>
+      <c r="H69">
+        <v>179.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>39.7</v>
+      </c>
+      <c r="K69">
+        <v>-1.52</v>
+      </c>
+      <c r="L69">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M69">
+        <v>6.370494000000001</v>
+      </c>
+      <c r="N69">
+        <v>34.84950600000001</v>
+      </c>
+      <c r="O69">
+        <v>12.1973271</v>
+      </c>
+      <c r="P69">
+        <v>22.6521789</v>
+      </c>
+      <c r="Q69">
+        <v>21.1321789</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.5544561195945716</v>
+      </c>
+      <c r="T69">
+        <v>1.936659531184133</v>
+      </c>
+      <c r="U69">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.35</v>
+      </c>
+      <c r="W69">
+        <v>0.03445</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>6.47045582336315</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2052304883517321</v>
+      </c>
+      <c r="C70">
+        <v>106.5822411109095</v>
+      </c>
+      <c r="D70">
+        <v>195.6742411109095</v>
+      </c>
+      <c r="E70">
+        <v>121.992</v>
+      </c>
+      <c r="F70">
+        <v>121.992</v>
+      </c>
+      <c r="G70">
+        <v>32.9</v>
+      </c>
+      <c r="H70">
+        <v>179.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>39.7</v>
+      </c>
+      <c r="K70">
+        <v>-1.52</v>
+      </c>
+      <c r="L70">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M70">
+        <v>6.465576000000001</v>
+      </c>
+      <c r="N70">
+        <v>34.75442400000001</v>
+      </c>
+      <c r="O70">
+        <v>12.1640484</v>
+      </c>
+      <c r="P70">
+        <v>22.59037560000001</v>
+      </c>
+      <c r="Q70">
+        <v>21.07037560000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.568139026099163</v>
+      </c>
+      <c r="T70">
+        <v>1.988048684322184</v>
+      </c>
+      <c r="U70">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.35</v>
+      </c>
+      <c r="W70">
+        <v>0.03445</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>6.375302061254867</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2044089572372557</v>
+      </c>
+      <c r="C71">
+        <v>105.7589161278645</v>
+      </c>
+      <c r="D71">
+        <v>196.6449161278645</v>
+      </c>
+      <c r="E71">
+        <v>123.786</v>
+      </c>
+      <c r="F71">
+        <v>123.786</v>
+      </c>
+      <c r="G71">
+        <v>32.9</v>
+      </c>
+      <c r="H71">
+        <v>179.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>39.7</v>
+      </c>
+      <c r="K71">
+        <v>-1.52</v>
+      </c>
+      <c r="L71">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M71">
+        <v>6.560658000000002</v>
+      </c>
+      <c r="N71">
+        <v>34.659342</v>
+      </c>
+      <c r="O71">
+        <v>12.1307697</v>
+      </c>
+      <c r="P71">
+        <v>22.5285723</v>
+      </c>
+      <c r="Q71">
+        <v>21.0085723</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.582704700765341</v>
+      </c>
+      <c r="T71">
+        <v>2.042753266694947</v>
+      </c>
+      <c r="U71">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.35</v>
+      </c>
+      <c r="W71">
+        <v>0.03445</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>6.282906379207694</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2044974261227792</v>
+      </c>
+      <c r="C72">
+        <v>103.8599238115638</v>
+      </c>
+      <c r="D72">
+        <v>196.5399238115638</v>
+      </c>
+      <c r="E72">
+        <v>125.58</v>
+      </c>
+      <c r="F72">
+        <v>125.58</v>
+      </c>
+      <c r="G72">
+        <v>32.9</v>
+      </c>
+      <c r="H72">
+        <v>179.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>39.7</v>
+      </c>
+      <c r="K72">
+        <v>-1.52</v>
+      </c>
+      <c r="L72">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M72">
+        <v>6.906900000000001</v>
+      </c>
+      <c r="N72">
+        <v>34.31310000000001</v>
+      </c>
+      <c r="O72">
+        <v>12.009585</v>
+      </c>
+      <c r="P72">
+        <v>22.303515</v>
+      </c>
+      <c r="Q72">
+        <v>20.783515</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.5982414204092641</v>
+      </c>
+      <c r="T72">
+        <v>2.101104821225895</v>
+      </c>
+      <c r="U72">
+        <v>0.055</v>
+      </c>
+      <c r="V72">
+        <v>0.35</v>
+      </c>
+      <c r="W72">
+        <v>0.03575</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>5.967945098379881</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2036888950083028</v>
+      </c>
+      <c r="C73">
+        <v>103.0296554420686</v>
+      </c>
+      <c r="D73">
+        <v>197.5036554420686</v>
+      </c>
+      <c r="E73">
+        <v>127.374</v>
+      </c>
+      <c r="F73">
+        <v>127.374</v>
+      </c>
+      <c r="G73">
+        <v>32.9</v>
+      </c>
+      <c r="H73">
+        <v>179.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>39.7</v>
+      </c>
+      <c r="K73">
+        <v>-1.52</v>
+      </c>
+      <c r="L73">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M73">
+        <v>7.00557</v>
+      </c>
+      <c r="N73">
+        <v>34.21443000000001</v>
+      </c>
+      <c r="O73">
+        <v>11.9750505</v>
+      </c>
+      <c r="P73">
+        <v>22.23937950000001</v>
+      </c>
+      <c r="Q73">
+        <v>20.71937950000001</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.6148496379596646</v>
+      </c>
+      <c r="T73">
+        <v>2.163480620896908</v>
+      </c>
+      <c r="U73">
+        <v>0.055</v>
+      </c>
+      <c r="V73">
+        <v>0.35</v>
+      </c>
+      <c r="W73">
+        <v>0.03575</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>5.883889533613968</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2028803638938263</v>
+      </c>
+      <c r="C74">
+        <v>102.2088849428947</v>
+      </c>
+      <c r="D74">
+        <v>198.4768849428947</v>
+      </c>
+      <c r="E74">
+        <v>129.168</v>
+      </c>
+      <c r="F74">
+        <v>129.168</v>
+      </c>
+      <c r="G74">
+        <v>32.9</v>
+      </c>
+      <c r="H74">
+        <v>179.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>39.7</v>
+      </c>
+      <c r="K74">
+        <v>-1.52</v>
+      </c>
+      <c r="L74">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M74">
+        <v>7.104240000000001</v>
+      </c>
+      <c r="N74">
+        <v>34.11576000000001</v>
+      </c>
+      <c r="O74">
+        <v>11.940516</v>
+      </c>
+      <c r="P74">
+        <v>22.17524400000001</v>
+      </c>
+      <c r="Q74">
+        <v>20.65524400000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.6326441567636651</v>
+      </c>
+      <c r="T74">
+        <v>2.230311834830136</v>
+      </c>
+      <c r="U74">
+        <v>0.055</v>
+      </c>
+      <c r="V74">
+        <v>0.35</v>
+      </c>
+      <c r="W74">
+        <v>0.03575</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>5.802168845647107</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2020718327793498</v>
+      </c>
+      <c r="C75">
+        <v>101.397753415974</v>
+      </c>
+      <c r="D75">
+        <v>199.459753415974</v>
+      </c>
+      <c r="E75">
+        <v>130.962</v>
+      </c>
+      <c r="F75">
+        <v>130.962</v>
+      </c>
+      <c r="G75">
+        <v>32.9</v>
+      </c>
+      <c r="H75">
+        <v>179.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>39.7</v>
+      </c>
+      <c r="K75">
+        <v>-1.52</v>
+      </c>
+      <c r="L75">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M75">
+        <v>7.202909999999999</v>
+      </c>
+      <c r="N75">
+        <v>34.01709000000001</v>
+      </c>
+      <c r="O75">
+        <v>11.9059815</v>
+      </c>
+      <c r="P75">
+        <v>22.11110850000001</v>
+      </c>
+      <c r="Q75">
+        <v>20.59110850000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.6517567880716659</v>
+      </c>
+      <c r="T75">
+        <v>2.302093509054714</v>
+      </c>
+      <c r="U75">
+        <v>0.055</v>
+      </c>
+      <c r="V75">
+        <v>0.35</v>
+      </c>
+      <c r="W75">
+        <v>0.03575</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>5.722687080638244</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2012633016648733</v>
+      </c>
+      <c r="C76">
+        <v>100.5964047721263</v>
+      </c>
+      <c r="D76">
+        <v>200.4524047721263</v>
+      </c>
+      <c r="E76">
+        <v>132.756</v>
+      </c>
+      <c r="F76">
+        <v>132.756</v>
+      </c>
+      <c r="G76">
+        <v>32.9</v>
+      </c>
+      <c r="H76">
+        <v>179.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>39.7</v>
+      </c>
+      <c r="K76">
+        <v>-1.52</v>
+      </c>
+      <c r="L76">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M76">
+        <v>7.30158</v>
+      </c>
+      <c r="N76">
+        <v>33.91842</v>
+      </c>
+      <c r="O76">
+        <v>11.871447</v>
+      </c>
+      <c r="P76">
+        <v>22.046973</v>
+      </c>
+      <c r="Q76">
+        <v>20.526973</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.6723396217879742</v>
+      </c>
+      <c r="T76">
+        <v>2.379396850527337</v>
+      </c>
+      <c r="U76">
+        <v>0.055</v>
+      </c>
+      <c r="V76">
+        <v>0.35</v>
+      </c>
+      <c r="W76">
+        <v>0.03575</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>5.645353471440428</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2004547705503969</v>
+      </c>
+      <c r="C77">
+        <v>99.8049858013039</v>
+      </c>
+      <c r="D77">
+        <v>201.4549858013039</v>
+      </c>
+      <c r="E77">
+        <v>134.55</v>
+      </c>
+      <c r="F77">
+        <v>134.55</v>
+      </c>
+      <c r="G77">
+        <v>32.9</v>
+      </c>
+      <c r="H77">
+        <v>179.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>39.7</v>
+      </c>
+      <c r="K77">
+        <v>-1.52</v>
+      </c>
+      <c r="L77">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M77">
+        <v>7.400250000000001</v>
+      </c>
+      <c r="N77">
+        <v>33.81975000000001</v>
+      </c>
+      <c r="O77">
+        <v>11.8369125</v>
+      </c>
+      <c r="P77">
+        <v>21.9828375</v>
+      </c>
+      <c r="Q77">
+        <v>20.4628375</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.6945690822015875</v>
+      </c>
+      <c r="T77">
+        <v>2.46288445931777</v>
+      </c>
+      <c r="U77">
+        <v>0.055</v>
+      </c>
+      <c r="V77">
+        <v>0.35</v>
+      </c>
+      <c r="W77">
+        <v>0.03575</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>5.570082091821223</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1996462394359205</v>
+      </c>
+      <c r="C78">
+        <v>99.02364624495485</v>
+      </c>
+      <c r="D78">
+        <v>202.4676462449548</v>
+      </c>
+      <c r="E78">
+        <v>136.344</v>
+      </c>
+      <c r="F78">
+        <v>136.344</v>
+      </c>
+      <c r="G78">
+        <v>32.9</v>
+      </c>
+      <c r="H78">
+        <v>179.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>39.7</v>
+      </c>
+      <c r="K78">
+        <v>-1.52</v>
+      </c>
+      <c r="L78">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M78">
+        <v>7.49892</v>
+      </c>
+      <c r="N78">
+        <v>33.72108000000001</v>
+      </c>
+      <c r="O78">
+        <v>11.802378</v>
+      </c>
+      <c r="P78">
+        <v>21.918702</v>
+      </c>
+      <c r="Q78">
+        <v>20.398702</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.7186509976496687</v>
+      </c>
+      <c r="T78">
+        <v>2.553329368840739</v>
+      </c>
+      <c r="U78">
+        <v>0.055</v>
+      </c>
+      <c r="V78">
+        <v>0.35</v>
+      </c>
+      <c r="W78">
+        <v>0.03575</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>5.49679153798147</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.198837708321444</v>
+      </c>
+      <c r="C79">
+        <v>98.25253887057943</v>
+      </c>
+      <c r="D79">
+        <v>203.4905388705794</v>
+      </c>
+      <c r="E79">
+        <v>138.138</v>
+      </c>
+      <c r="F79">
+        <v>138.138</v>
+      </c>
+      <c r="G79">
+        <v>32.9</v>
+      </c>
+      <c r="H79">
+        <v>179.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>39.7</v>
+      </c>
+      <c r="K79">
+        <v>-1.52</v>
+      </c>
+      <c r="L79">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M79">
+        <v>7.59759</v>
+      </c>
+      <c r="N79">
+        <v>33.62241</v>
+      </c>
+      <c r="O79">
+        <v>11.7678435</v>
+      </c>
+      <c r="P79">
+        <v>21.8545665</v>
+      </c>
+      <c r="Q79">
+        <v>20.3345665</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.7448269927019304</v>
+      </c>
+      <c r="T79">
+        <v>2.651639053104836</v>
+      </c>
+      <c r="U79">
+        <v>0.055</v>
+      </c>
+      <c r="V79">
+        <v>0.35</v>
+      </c>
+      <c r="W79">
+        <v>0.03575</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>5.425404634890801</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1980291772069675</v>
+      </c>
+      <c r="C80">
+        <v>97.49181954855842</v>
+      </c>
+      <c r="D80">
+        <v>204.5238195485584</v>
+      </c>
+      <c r="E80">
+        <v>139.932</v>
+      </c>
+      <c r="F80">
+        <v>139.932</v>
+      </c>
+      <c r="G80">
+        <v>32.9</v>
+      </c>
+      <c r="H80">
+        <v>179.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>39.7</v>
+      </c>
+      <c r="K80">
+        <v>-1.52</v>
+      </c>
+      <c r="L80">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M80">
+        <v>7.696260000000001</v>
+      </c>
+      <c r="N80">
+        <v>33.52374</v>
+      </c>
+      <c r="O80">
+        <v>11.733309</v>
+      </c>
+      <c r="P80">
+        <v>21.79043100000001</v>
+      </c>
+      <c r="Q80">
+        <v>20.27043100000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.7733826236680341</v>
+      </c>
+      <c r="T80">
+        <v>2.758885981392941</v>
+      </c>
+      <c r="U80">
+        <v>0.055</v>
+      </c>
+      <c r="V80">
+        <v>0.35</v>
+      </c>
+      <c r="W80">
+        <v>0.03575</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>5.355848165212714</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1972206460924911</v>
+      </c>
+      <c r="C81">
+        <v>96.74164733133378</v>
+      </c>
+      <c r="D81">
+        <v>205.5676473313338</v>
+      </c>
+      <c r="E81">
+        <v>141.726</v>
+      </c>
+      <c r="F81">
+        <v>141.726</v>
+      </c>
+      <c r="G81">
+        <v>32.9</v>
+      </c>
+      <c r="H81">
+        <v>179.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>39.7</v>
+      </c>
+      <c r="K81">
+        <v>-1.52</v>
+      </c>
+      <c r="L81">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M81">
+        <v>7.79493</v>
+      </c>
+      <c r="N81">
+        <v>33.42507000000001</v>
+      </c>
+      <c r="O81">
+        <v>11.6987745</v>
+      </c>
+      <c r="P81">
+        <v>21.72629550000001</v>
+      </c>
+      <c r="Q81">
+        <v>20.20629550000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.804657838535672</v>
+      </c>
+      <c r="T81">
+        <v>2.876346902851343</v>
+      </c>
+      <c r="U81">
+        <v>0.055</v>
+      </c>
+      <c r="V81">
+        <v>0.35</v>
+      </c>
+      <c r="W81">
+        <v>0.03575</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>5.288052618817617</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1964121149780146</v>
+      </c>
+      <c r="C82">
+        <v>96.00218453502714</v>
+      </c>
+      <c r="D82">
+        <v>206.6221845350271</v>
+      </c>
+      <c r="E82">
+        <v>143.52</v>
+      </c>
+      <c r="F82">
+        <v>143.52</v>
+      </c>
+      <c r="G82">
+        <v>32.9</v>
+      </c>
+      <c r="H82">
+        <v>179.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>39.7</v>
+      </c>
+      <c r="K82">
+        <v>-1.52</v>
+      </c>
+      <c r="L82">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M82">
+        <v>7.8936</v>
+      </c>
+      <c r="N82">
+        <v>33.32640000000001</v>
+      </c>
+      <c r="O82">
+        <v>11.66424</v>
+      </c>
+      <c r="P82">
+        <v>21.66216000000001</v>
+      </c>
+      <c r="Q82">
+        <v>20.14216000000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.839060574890073</v>
+      </c>
+      <c r="T82">
+        <v>3.005553916455584</v>
+      </c>
+      <c r="U82">
+        <v>0.055</v>
+      </c>
+      <c r="V82">
+        <v>0.35</v>
+      </c>
+      <c r="W82">
+        <v>0.03575</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>5.221951961082397</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1956035838635381</v>
+      </c>
+      <c r="C83">
+        <v>95.27359682358207</v>
+      </c>
+      <c r="D83">
+        <v>207.6875968235821</v>
+      </c>
+      <c r="E83">
+        <v>145.314</v>
+      </c>
+      <c r="F83">
+        <v>145.314</v>
+      </c>
+      <c r="G83">
+        <v>32.9</v>
+      </c>
+      <c r="H83">
+        <v>179.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>39.7</v>
+      </c>
+      <c r="K83">
+        <v>-1.52</v>
+      </c>
+      <c r="L83">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M83">
+        <v>7.992270000000001</v>
+      </c>
+      <c r="N83">
+        <v>33.22773000000001</v>
+      </c>
+      <c r="O83">
+        <v>11.6297055</v>
+      </c>
+      <c r="P83">
+        <v>21.59802450000001</v>
+      </c>
+      <c r="Q83">
+        <v>20.07802450000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.8770846519133588</v>
+      </c>
+      <c r="T83">
+        <v>3.148361668333957</v>
+      </c>
+      <c r="U83">
+        <v>0.055</v>
+      </c>
+      <c r="V83">
+        <v>0.35</v>
+      </c>
+      <c r="W83">
+        <v>0.03575</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>5.157483418352984</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1947950527490617</v>
+      </c>
+      <c r="C84">
+        <v>94.55605329552441</v>
+      </c>
+      <c r="D84">
+        <v>208.7640532955244</v>
+      </c>
+      <c r="E84">
+        <v>147.108</v>
+      </c>
+      <c r="F84">
+        <v>147.108</v>
+      </c>
+      <c r="G84">
+        <v>32.9</v>
+      </c>
+      <c r="H84">
+        <v>179.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>39.7</v>
+      </c>
+      <c r="K84">
+        <v>-1.52</v>
+      </c>
+      <c r="L84">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M84">
+        <v>8.09094</v>
+      </c>
+      <c r="N84">
+        <v>33.12906000000001</v>
+      </c>
+      <c r="O84">
+        <v>11.595171</v>
+      </c>
+      <c r="P84">
+        <v>21.53388900000001</v>
+      </c>
+      <c r="Q84">
+        <v>20.01388900000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.9193336263836762</v>
+      </c>
+      <c r="T84">
+        <v>3.307036948198815</v>
+      </c>
+      <c r="U84">
+        <v>0.055</v>
+      </c>
+      <c r="V84">
+        <v>0.35</v>
+      </c>
+      <c r="W84">
+        <v>0.03575</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>5.094587279104778</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1939865216345852</v>
+      </c>
+      <c r="C85">
+        <v>93.8497265734338</v>
+      </c>
+      <c r="D85">
+        <v>209.8517265734338</v>
+      </c>
+      <c r="E85">
+        <v>148.902</v>
+      </c>
+      <c r="F85">
+        <v>148.902</v>
+      </c>
+      <c r="G85">
+        <v>32.9</v>
+      </c>
+      <c r="H85">
+        <v>179.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>39.7</v>
+      </c>
+      <c r="K85">
+        <v>-1.52</v>
+      </c>
+      <c r="L85">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M85">
+        <v>8.18961</v>
+      </c>
+      <c r="N85">
+        <v>33.03039</v>
+      </c>
+      <c r="O85">
+        <v>11.5606365</v>
+      </c>
+      <c r="P85">
+        <v>21.4697535</v>
+      </c>
+      <c r="Q85">
+        <v>19.9497535</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.9665530684387371</v>
+      </c>
+      <c r="T85">
+        <v>3.484379908047774</v>
+      </c>
+      <c r="U85">
+        <v>0.055</v>
+      </c>
+      <c r="V85">
+        <v>0.35</v>
+      </c>
+      <c r="W85">
+        <v>0.03575</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>5.033206709477009</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1931779905201088</v>
+      </c>
+      <c r="C86">
+        <v>93.1547928962276</v>
+      </c>
+      <c r="D86">
+        <v>210.9507928962276</v>
+      </c>
+      <c r="E86">
+        <v>150.696</v>
+      </c>
+      <c r="F86">
+        <v>150.696</v>
+      </c>
+      <c r="G86">
+        <v>32.9</v>
+      </c>
+      <c r="H86">
+        <v>179.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>39.7</v>
+      </c>
+      <c r="K86">
+        <v>-1.52</v>
+      </c>
+      <c r="L86">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M86">
+        <v>8.28828</v>
+      </c>
+      <c r="N86">
+        <v>32.93172000000001</v>
+      </c>
+      <c r="O86">
+        <v>11.526102</v>
+      </c>
+      <c r="P86">
+        <v>21.405618</v>
+      </c>
+      <c r="Q86">
+        <v>19.885618</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>1.01967494075068</v>
+      </c>
+      <c r="T86">
+        <v>3.683890737877851</v>
+      </c>
+      <c r="U86">
+        <v>0.055</v>
+      </c>
+      <c r="V86">
+        <v>0.35</v>
+      </c>
+      <c r="W86">
+        <v>0.03575</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>4.973287581983234</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1923694594056323</v>
+      </c>
+      <c r="C87">
+        <v>92.47143221435897</v>
+      </c>
+      <c r="D87">
+        <v>212.061432214359</v>
+      </c>
+      <c r="E87">
+        <v>152.49</v>
+      </c>
+      <c r="F87">
+        <v>152.49</v>
+      </c>
+      <c r="G87">
+        <v>32.9</v>
+      </c>
+      <c r="H87">
+        <v>179.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>39.7</v>
+      </c>
+      <c r="K87">
+        <v>-1.52</v>
+      </c>
+      <c r="L87">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M87">
+        <v>8.386950000000001</v>
+      </c>
+      <c r="N87">
+        <v>32.83305000000001</v>
+      </c>
+      <c r="O87">
+        <v>11.4915675</v>
+      </c>
+      <c r="P87">
+        <v>21.34148250000001</v>
+      </c>
+      <c r="Q87">
+        <v>19.82148250000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>1.079879729370882</v>
+      </c>
+      <c r="T87">
+        <v>3.910003011685274</v>
+      </c>
+      <c r="U87">
+        <v>0.055</v>
+      </c>
+      <c r="V87">
+        <v>0.35</v>
+      </c>
+      <c r="W87">
+        <v>0.03575</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>4.914778316312844</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1915609282911558</v>
+      </c>
+      <c r="C88">
+        <v>91.79982828803927</v>
+      </c>
+      <c r="D88">
+        <v>213.1838282880393</v>
+      </c>
+      <c r="E88">
+        <v>154.284</v>
+      </c>
+      <c r="F88">
+        <v>154.284</v>
+      </c>
+      <c r="G88">
+        <v>32.9</v>
+      </c>
+      <c r="H88">
+        <v>179.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>39.7</v>
+      </c>
+      <c r="K88">
+        <v>-1.52</v>
+      </c>
+      <c r="L88">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M88">
+        <v>8.485619999999999</v>
+      </c>
+      <c r="N88">
+        <v>32.73438000000001</v>
+      </c>
+      <c r="O88">
+        <v>11.457033</v>
+      </c>
+      <c r="P88">
+        <v>21.27734700000001</v>
+      </c>
+      <c r="Q88">
+        <v>19.75734700000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>1.148685202079684</v>
+      </c>
+      <c r="T88">
+        <v>4.168417038893756</v>
+      </c>
+      <c r="U88">
+        <v>0.055</v>
+      </c>
+      <c r="V88">
+        <v>0.35</v>
+      </c>
+      <c r="W88">
+        <v>0.03575</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>4.85762973123944</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1907523971766794</v>
+      </c>
+      <c r="C89">
+        <v>91.14016878859539</v>
+      </c>
+      <c r="D89">
+        <v>214.3181687885954</v>
+      </c>
+      <c r="E89">
+        <v>156.078</v>
+      </c>
+      <c r="F89">
+        <v>156.078</v>
+      </c>
+      <c r="G89">
+        <v>32.9</v>
+      </c>
+      <c r="H89">
+        <v>179.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>39.7</v>
+      </c>
+      <c r="K89">
+        <v>-1.52</v>
+      </c>
+      <c r="L89">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M89">
+        <v>8.584290000000001</v>
+      </c>
+      <c r="N89">
+        <v>32.63571</v>
+      </c>
+      <c r="O89">
+        <v>11.4224985</v>
+      </c>
+      <c r="P89">
+        <v>21.2132115</v>
+      </c>
+      <c r="Q89">
+        <v>19.6932115</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.228076132128303</v>
+      </c>
+      <c r="T89">
+        <v>4.466587070288159</v>
+      </c>
+      <c r="U89">
+        <v>0.055</v>
+      </c>
+      <c r="V89">
+        <v>0.35</v>
+      </c>
+      <c r="W89">
+        <v>0.03575</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>4.801794906742433</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1899438660622029</v>
+      </c>
+      <c r="C90">
+        <v>90.4926454030805</v>
+      </c>
+      <c r="D90">
+        <v>215.4646454030805</v>
+      </c>
+      <c r="E90">
+        <v>157.872</v>
+      </c>
+      <c r="F90">
+        <v>157.872</v>
+      </c>
+      <c r="G90">
+        <v>32.9</v>
+      </c>
+      <c r="H90">
+        <v>179.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>39.7</v>
+      </c>
+      <c r="K90">
+        <v>-1.52</v>
+      </c>
+      <c r="L90">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M90">
+        <v>8.682960000000001</v>
+      </c>
+      <c r="N90">
+        <v>32.53704</v>
+      </c>
+      <c r="O90">
+        <v>11.387964</v>
+      </c>
+      <c r="P90">
+        <v>21.149076</v>
+      </c>
+      <c r="Q90">
+        <v>19.629076</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.320698883851691</v>
+      </c>
+      <c r="T90">
+        <v>4.814452106914964</v>
+      </c>
+      <c r="U90">
+        <v>0.055</v>
+      </c>
+      <c r="V90">
+        <v>0.35</v>
+      </c>
+      <c r="W90">
+        <v>0.03575</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>4.74722905552945</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1891353349477264</v>
+      </c>
+      <c r="C91">
+        <v>89.85745394226137</v>
+      </c>
+      <c r="D91">
+        <v>216.6234539422614</v>
+      </c>
+      <c r="E91">
+        <v>159.666</v>
+      </c>
+      <c r="F91">
+        <v>159.666</v>
+      </c>
+      <c r="G91">
+        <v>32.9</v>
+      </c>
+      <c r="H91">
+        <v>179.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>39.7</v>
+      </c>
+      <c r="K91">
+        <v>-1.52</v>
+      </c>
+      <c r="L91">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M91">
+        <v>8.78163</v>
+      </c>
+      <c r="N91">
+        <v>32.43837000000001</v>
+      </c>
+      <c r="O91">
+        <v>11.3534295</v>
+      </c>
+      <c r="P91">
+        <v>21.08494050000001</v>
+      </c>
+      <c r="Q91">
+        <v>19.56494050000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.430162135888422</v>
+      </c>
+      <c r="T91">
+        <v>5.225565332019368</v>
+      </c>
+      <c r="U91">
+        <v>0.055</v>
+      </c>
+      <c r="V91">
+        <v>0.35</v>
+      </c>
+      <c r="W91">
+        <v>0.03575</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>4.693889403220131</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.18832680383325</v>
+      </c>
+      <c r="C92">
+        <v>89.23479445210728</v>
+      </c>
+      <c r="D92">
+        <v>217.7947944521073</v>
+      </c>
+      <c r="E92">
+        <v>161.46</v>
+      </c>
+      <c r="F92">
+        <v>161.46</v>
+      </c>
+      <c r="G92">
+        <v>32.9</v>
+      </c>
+      <c r="H92">
+        <v>179.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>39.7</v>
+      </c>
+      <c r="K92">
+        <v>-1.52</v>
+      </c>
+      <c r="L92">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M92">
+        <v>8.8803</v>
+      </c>
+      <c r="N92">
+        <v>32.33970000000001</v>
+      </c>
+      <c r="O92">
+        <v>11.318895</v>
+      </c>
+      <c r="P92">
+        <v>21.02080500000001</v>
+      </c>
+      <c r="Q92">
+        <v>19.50080500000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.5615180383325</v>
+      </c>
+      <c r="T92">
+        <v>5.718901202144654</v>
+      </c>
+      <c r="U92">
+        <v>0.055</v>
+      </c>
+      <c r="V92">
+        <v>0.35</v>
+      </c>
+      <c r="W92">
+        <v>0.03575</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>4.641735076517686</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1875182727187735</v>
+      </c>
+      <c r="C93">
+        <v>88.62487132891803</v>
+      </c>
+      <c r="D93">
+        <v>218.978871328918</v>
+      </c>
+      <c r="E93">
+        <v>163.254</v>
+      </c>
+      <c r="F93">
+        <v>163.254</v>
+      </c>
+      <c r="G93">
+        <v>32.9</v>
+      </c>
+      <c r="H93">
+        <v>179.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>39.7</v>
+      </c>
+      <c r="K93">
+        <v>-1.52</v>
+      </c>
+      <c r="L93">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M93">
+        <v>8.97897</v>
+      </c>
+      <c r="N93">
+        <v>32.24103000000001</v>
+      </c>
+      <c r="O93">
+        <v>11.2843605</v>
+      </c>
+      <c r="P93">
+        <v>20.95666950000001</v>
+      </c>
+      <c r="Q93">
+        <v>19.43666950000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.722064141319706</v>
+      </c>
+      <c r="T93">
+        <v>6.321867265631115</v>
+      </c>
+      <c r="U93">
+        <v>0.055</v>
+      </c>
+      <c r="V93">
+        <v>0.35</v>
+      </c>
+      <c r="W93">
+        <v>0.03575</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>4.590726998753755</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1867097416042971</v>
+      </c>
+      <c r="C94">
+        <v>88.02789343822596</v>
+      </c>
+      <c r="D94">
+        <v>220.175893438226</v>
+      </c>
+      <c r="E94">
+        <v>165.048</v>
+      </c>
+      <c r="F94">
+        <v>165.048</v>
+      </c>
+      <c r="G94">
+        <v>32.9</v>
+      </c>
+      <c r="H94">
+        <v>179.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>39.7</v>
+      </c>
+      <c r="K94">
+        <v>-1.52</v>
+      </c>
+      <c r="L94">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M94">
+        <v>9.077640000000001</v>
+      </c>
+      <c r="N94">
+        <v>32.14236</v>
+      </c>
+      <c r="O94">
+        <v>11.249826</v>
+      </c>
+      <c r="P94">
+        <v>20.892534</v>
+      </c>
+      <c r="Q94">
+        <v>19.37253400000001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.922746770053714</v>
+      </c>
+      <c r="T94">
+        <v>7.075574844989191</v>
+      </c>
+      <c r="U94">
+        <v>0.055</v>
+      </c>
+      <c r="V94">
+        <v>0.35</v>
+      </c>
+      <c r="W94">
+        <v>0.03575</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>4.540827792245562</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1881983104898206</v>
+      </c>
+      <c r="C95">
+        <v>84.04011371447987</v>
+      </c>
+      <c r="D95">
+        <v>217.9821137144799</v>
+      </c>
+      <c r="E95">
+        <v>166.842</v>
+      </c>
+      <c r="F95">
+        <v>166.842</v>
+      </c>
+      <c r="G95">
+        <v>32.9</v>
+      </c>
+      <c r="H95">
+        <v>179.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>39.7</v>
+      </c>
+      <c r="K95">
+        <v>-1.52</v>
+      </c>
+      <c r="L95">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M95">
+        <v>9.810309600000002</v>
+      </c>
+      <c r="N95">
+        <v>31.4096904</v>
+      </c>
+      <c r="O95">
+        <v>10.99339164</v>
+      </c>
+      <c r="P95">
+        <v>20.41629876</v>
+      </c>
+      <c r="Q95">
+        <v>18.89629876</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>2.180767292711725</v>
+      </c>
+      <c r="T95">
+        <v>8.044627447021002</v>
+      </c>
+      <c r="U95">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V95">
+        <v>0.35</v>
+      </c>
+      <c r="W95">
+        <v>0.03822</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>4.20170225820396</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1874144793753442</v>
+      </c>
+      <c r="C96">
+        <v>83.39580763291173</v>
+      </c>
+      <c r="D96">
+        <v>219.1318076329117</v>
+      </c>
+      <c r="E96">
+        <v>168.636</v>
+      </c>
+      <c r="F96">
+        <v>168.636</v>
+      </c>
+      <c r="G96">
+        <v>32.9</v>
+      </c>
+      <c r="H96">
+        <v>179.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>39.7</v>
+      </c>
+      <c r="K96">
+        <v>-1.52</v>
+      </c>
+      <c r="L96">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M96">
+        <v>9.915796800000003</v>
+      </c>
+      <c r="N96">
+        <v>31.3042032</v>
+      </c>
+      <c r="O96">
+        <v>10.95647112</v>
+      </c>
+      <c r="P96">
+        <v>20.34773208</v>
+      </c>
+      <c r="Q96">
+        <v>18.82773208</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.524794656255739</v>
+      </c>
+      <c r="T96">
+        <v>9.336697583063421</v>
+      </c>
+      <c r="U96">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V96">
+        <v>0.35</v>
+      </c>
+      <c r="W96">
+        <v>0.03822</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>4.157003298010302</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1866306482608677</v>
+      </c>
+      <c r="C97">
+        <v>82.76369341921392</v>
+      </c>
+      <c r="D97">
+        <v>220.2936934192139</v>
+      </c>
+      <c r="E97">
+        <v>170.43</v>
+      </c>
+      <c r="F97">
+        <v>170.43</v>
+      </c>
+      <c r="G97">
+        <v>32.9</v>
+      </c>
+      <c r="H97">
+        <v>179.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>39.7</v>
+      </c>
+      <c r="K97">
+        <v>-1.52</v>
+      </c>
+      <c r="L97">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M97">
+        <v>10.021284</v>
+      </c>
+      <c r="N97">
+        <v>31.198716</v>
+      </c>
+      <c r="O97">
+        <v>10.9195506</v>
+      </c>
+      <c r="P97">
+        <v>20.2791654</v>
+      </c>
+      <c r="Q97">
+        <v>18.7591654</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>3.006432965217358</v>
+      </c>
+      <c r="T97">
+        <v>11.14559577352281</v>
+      </c>
+      <c r="U97">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V97">
+        <v>0.35</v>
+      </c>
+      <c r="W97">
+        <v>0.03822</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>4.113245368557562</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1858468171463913</v>
+      </c>
+      <c r="C98">
+        <v>82.14396603915799</v>
+      </c>
+      <c r="D98">
+        <v>221.467966039158</v>
+      </c>
+      <c r="E98">
+        <v>172.224</v>
+      </c>
+      <c r="F98">
+        <v>172.224</v>
+      </c>
+      <c r="G98">
+        <v>32.9</v>
+      </c>
+      <c r="H98">
+        <v>179.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>39.7</v>
+      </c>
+      <c r="K98">
+        <v>-1.52</v>
+      </c>
+      <c r="L98">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M98">
+        <v>10.1267712</v>
+      </c>
+      <c r="N98">
+        <v>31.09322880000001</v>
+      </c>
+      <c r="O98">
+        <v>10.88263008</v>
+      </c>
+      <c r="P98">
+        <v>20.21059872</v>
+      </c>
+      <c r="Q98">
+        <v>18.69059872</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.728890428659778</v>
+      </c>
+      <c r="T98">
+        <v>13.85894305921185</v>
+      </c>
+      <c r="U98">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V98">
+        <v>0.35</v>
+      </c>
+      <c r="W98">
+        <v>0.03822</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>4.070399062635088</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.1850629860319148</v>
+      </c>
+      <c r="C99">
+        <v>81.53682463784284</v>
+      </c>
+      <c r="D99">
+        <v>222.6548246378428</v>
+      </c>
+      <c r="E99">
+        <v>174.018</v>
+      </c>
+      <c r="F99">
+        <v>174.018</v>
+      </c>
+      <c r="G99">
+        <v>32.9</v>
+      </c>
+      <c r="H99">
+        <v>179.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>39.7</v>
+      </c>
+      <c r="K99">
+        <v>-1.52</v>
+      </c>
+      <c r="L99">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M99">
+        <v>10.2322584</v>
+      </c>
+      <c r="N99">
+        <v>30.98774160000001</v>
+      </c>
+      <c r="O99">
+        <v>10.84570956</v>
+      </c>
+      <c r="P99">
+        <v>20.14203204</v>
+      </c>
+      <c r="Q99">
+        <v>18.62203204</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.932986201063823</v>
+      </c>
+      <c r="T99">
+        <v>18.38118853536029</v>
+      </c>
+      <c r="U99">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V99">
+        <v>0.35</v>
+      </c>
+      <c r="W99">
+        <v>0.03822</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>4.028436185700706</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1869545549174383</v>
+      </c>
+      <c r="C100">
+        <v>76.900070739852</v>
+      </c>
+      <c r="D100">
+        <v>219.812070739852</v>
+      </c>
+      <c r="E100">
+        <v>175.812</v>
+      </c>
+      <c r="F100">
+        <v>175.812</v>
+      </c>
+      <c r="G100">
+        <v>32.9</v>
+      </c>
+      <c r="H100">
+        <v>179.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>39.7</v>
+      </c>
+      <c r="K100">
+        <v>-1.52</v>
+      </c>
+      <c r="L100">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M100">
+        <v>11.076156</v>
+      </c>
+      <c r="N100">
+        <v>30.143844</v>
+      </c>
+      <c r="O100">
+        <v>10.5503454</v>
+      </c>
+      <c r="P100">
+        <v>19.5934986</v>
+      </c>
+      <c r="Q100">
+        <v>18.0734986</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>7.34117774587191</v>
+      </c>
+      <c r="T100">
+        <v>27.42567948765718</v>
+      </c>
+      <c r="U100">
+        <v>0.063</v>
+      </c>
+      <c r="V100">
+        <v>0.35</v>
+      </c>
+      <c r="W100">
+        <v>0.04095</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>3.721507714409223</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1861980238029619</v>
+      </c>
+      <c r="C101">
+        <v>76.23427223510745</v>
+      </c>
+      <c r="D101">
+        <v>220.9402722351074</v>
+      </c>
+      <c r="E101">
+        <v>177.606</v>
+      </c>
+      <c r="F101">
+        <v>177.606</v>
+      </c>
+      <c r="G101">
+        <v>32.9</v>
+      </c>
+      <c r="H101">
+        <v>179.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>39.7</v>
+      </c>
+      <c r="K101">
+        <v>-1.52</v>
+      </c>
+      <c r="L101">
+        <v>41.22000000000001</v>
+      </c>
+      <c r="M101">
+        <v>11.189178</v>
+      </c>
+      <c r="N101">
+        <v>30.03082200000001</v>
+      </c>
+      <c r="O101">
+        <v>10.5107877</v>
+      </c>
+      <c r="P101">
+        <v>19.52003430000001</v>
+      </c>
+      <c r="Q101">
+        <v>18.00003430000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>14.56575238029618</v>
+      </c>
+      <c r="T101">
+        <v>54.55915234454785</v>
+      </c>
+      <c r="U101">
+        <v>0.063</v>
+      </c>
+      <c r="V101">
+        <v>0.35</v>
+      </c>
+      <c r="W101">
+        <v>0.04095</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>3.683916727394989</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
